--- a/Models/Яйца/results/Яйца - Результаты прогнозов Prophet.xlsx
+++ b/Models/Яйца/results/Яйца - Результаты прогнозов Prophet.xlsx
@@ -478,31 +478,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5469.43</v>
+        <v>4604.18</v>
       </c>
       <c r="E2" t="n">
-        <v>5068.56</v>
+        <v>4236.18</v>
       </c>
       <c r="F2" t="n">
-        <v>9.23</v>
+        <v>7.11</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[50733.78, 51554.24, 56222.54]</t>
+          <t>[56647.38, 56425.12, 51490.48]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[46739.2, 48287.8, 64167.2]</t>
+          <t>[62899.9, 58300.1, 56071.5]</t>
         </is>
       </c>
     </row>
@@ -514,31 +514,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6215.98</v>
+        <v>2613.77</v>
       </c>
       <c r="E3" t="n">
-        <v>5769.11</v>
+        <v>2221.52</v>
       </c>
       <c r="F3" t="n">
-        <v>9.720000000000001</v>
+        <v>3.98</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[51229.08, 55557.27, 53907.47]</t>
+          <t>[56858.09, 51914.52, 51148.14]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[48287.8, 64167.2, 59663.6]</t>
+          <t>[58300.1, 56071.5, 52213.7]</t>
         </is>
       </c>
     </row>
@@ -550,31 +550,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6612.81</v>
+        <v>2952.35</v>
       </c>
       <c r="E4" t="n">
-        <v>6091.37</v>
+        <v>2640.49</v>
       </c>
       <c r="F4" t="n">
-        <v>9.82</v>
+        <v>4.77</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[55022.53, 53382.86, 57862.89]</t>
+          <t>[51836.33, 51212.59, 52955.1]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[64167.2, 59663.6, 60711.6]</t>
+          <t>[56071.5, 52213.7, 55640.3]</t>
         </is>
       </c>
     </row>
@@ -586,31 +586,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3589.61</v>
+        <v>2218.22</v>
       </c>
       <c r="E5" t="n">
-        <v>3014.11</v>
+        <v>2025.89</v>
       </c>
       <c r="F5" t="n">
-        <v>5.02</v>
+        <v>3.72</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[53936.22, 58630.69, 59533.57]</t>
+          <t>[51412.91, 53316.07, 51376.35]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[59663.6, 60711.6, 60767.6]</t>
+          <t>[52213.7, 55640.3, 54329.0]</t>
         </is>
       </c>
     </row>
@@ -622,31 +622,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3916.02</v>
+        <v>2042.66</v>
       </c>
       <c r="E6" t="n">
-        <v>3005.81</v>
+        <v>1968.7</v>
       </c>
       <c r="F6" t="n">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>[58965.96, 60005.61, 57760.49]</t>
+          <t>[53626.92, 51716.65, 46411.97]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[60711.6, 60767.6, 64270.3]</t>
+          <t>[55640.3, 54329.0, 45131.6]</t>
         </is>
       </c>
     </row>
@@ -658,31 +658,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5386.85</v>
+        <v>3216.31</v>
       </c>
       <c r="E7" t="n">
-        <v>4593.21</v>
+        <v>2909.28</v>
       </c>
       <c r="F7" t="n">
-        <v>7.24</v>
+        <v>5.26</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>[60148.33, 57881.85, 56128.0]</t>
+          <t>[51974.85, 46709.09, 55588.6]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[60767.6, 64270.3, 62899.9]</t>
+          <t>[54329.0, 45131.6, 60384.8]</t>
         </is>
       </c>
     </row>
@@ -694,31 +694,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5559.95</v>
+        <v>2950.72</v>
       </c>
       <c r="E8" t="n">
-        <v>5207.7</v>
+        <v>2638.97</v>
       </c>
       <c r="F8" t="n">
-        <v>8.31</v>
+        <v>4.83</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>[57956.7, 56060.66, 55829.83]</t>
+          <t>[46941.39, 55882.72, 54666.54]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[64270.3, 62899.9, 58300.1]</t>
+          <t>[45131.6, 60384.8, 53061.5]</t>
         </is>
       </c>
     </row>
@@ -730,31 +730,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4604.18</v>
+        <v>3263.77</v>
       </c>
       <c r="E9" t="n">
-        <v>4236.18</v>
+        <v>2966.64</v>
       </c>
       <c r="F9" t="n">
-        <v>7.11</v>
+        <v>4.97</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>[56647.38, 56425.12, 51490.48]</t>
+          <t>[55674.04, 54452.22, 59441.36]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[62899.9, 58300.1, 56071.5]</t>
+          <t>[60384.8, 53061.5, 62239.8]</t>
         </is>
       </c>
     </row>
@@ -766,31 +766,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2613.77</v>
+        <v>1759.71</v>
       </c>
       <c r="E10" t="n">
-        <v>2221.52</v>
+        <v>1691.44</v>
       </c>
       <c r="F10" t="n">
-        <v>3.98</v>
+        <v>2.91</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>[56858.09, 51914.52, 51148.14]</t>
+          <t>[55138.48, 60249.3, 60799.55]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[58300.1, 56071.5, 52213.7]</t>
+          <t>[53061.5, 62239.8, 61806.4]</t>
         </is>
       </c>
     </row>
@@ -802,31 +802,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2952.35</v>
+        <v>2052.53</v>
       </c>
       <c r="E11" t="n">
-        <v>2640.49</v>
+        <v>1978.77</v>
       </c>
       <c r="F11" t="n">
-        <v>4.77</v>
+        <v>3.18</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>[51836.33, 51212.59, 52955.1]</t>
+          <t>[60048.92, 60575.77, 59699.99]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[56071.5, 52213.7, 55640.3]</t>
+          <t>[62239.8, 61806.4, 62214.8]</t>
         </is>
       </c>
     </row>
@@ -838,31 +838,31 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>260.32</v>
+        <v>1509.41</v>
       </c>
       <c r="E12" t="n">
-        <v>219.22</v>
+        <v>1466.99</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3</v>
+        <v>7.85</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>[17446.77, 14282.19, 15720.97]</t>
+          <t>[15940.87, 18024.69, 18015.68]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[17851.6, 14347.6, 15908.4]</t>
+          <t>[17751.9, 19636.9, 18993.4]</t>
         </is>
       </c>
     </row>
@@ -874,31 +874,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>455.52</v>
+        <v>1559.58</v>
       </c>
       <c r="E13" t="n">
-        <v>353.24</v>
+        <v>1464.03</v>
       </c>
       <c r="F13" t="n">
-        <v>2.31</v>
+        <v>7.61</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>[14259.47, 15689.76, 15951.44]</t>
+          <t>[18154.34, 18196.76, 16949.21]</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[14347.6, 15908.4, 15198.5]</t>
+          <t>[19636.9, 18993.4, 19062.1]</t>
         </is>
       </c>
     </row>
@@ -910,31 +910,31 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1188.93</v>
+        <v>2488.42</v>
       </c>
       <c r="E14" t="n">
-        <v>957.3200000000001</v>
+        <v>2130.27</v>
       </c>
       <c r="F14" t="n">
-        <v>5.85</v>
+        <v>11.28</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>[15662.43, 15906.42, 18814.08]</t>
+          <t>[18346.68, 17101.39, 14992.1]</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[15908.4, 15198.5, 16896.0]</t>
+          <t>[18993.4, 19062.1, 18775.5]</t>
         </is>
       </c>
     </row>
@@ -946,31 +946,31 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1412.1</v>
+        <v>3257.54</v>
       </c>
       <c r="E15" t="n">
-        <v>1317.52</v>
+        <v>3136.1</v>
       </c>
       <c r="F15" t="n">
-        <v>7.6</v>
+        <v>16.19</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>[15906.4, 18847.72, 18337.85]</t>
+          <t>[17170.81, 15066.46, 16340.62]</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[15198.5, 16896.0, 19630.8]</t>
+          <t>[19062.1, 18775.5, 20148.6]</t>
         </is>
       </c>
     </row>
@@ -982,31 +982,31 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2184.78</v>
+        <v>3541.9</v>
       </c>
       <c r="E16" t="n">
-        <v>2081.74</v>
+        <v>3534.04</v>
       </c>
       <c r="F16" t="n">
-        <v>10.95</v>
+        <v>18.89</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>[18700.09, 18185.86, 17246.0]</t>
+          <t>[15117.98, 16407.85, 13991.26]</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[16896.0, 19630.8, 20242.2]</t>
+          <t>[18775.5, 20148.6, 17195.1]</t>
         </is>
       </c>
     </row>
@@ -1018,31 +1018,31 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2446.84</v>
+        <v>3243.08</v>
       </c>
       <c r="E17" t="n">
-        <v>2360.19</v>
+        <v>3234.47</v>
       </c>
       <c r="F17" t="n">
-        <v>12.26</v>
+        <v>17.13</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>[17983.16, 17031.73, 15529.44]</t>
+          <t>[16672.72, 14281.14, 15968.04]</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[19630.8, 20242.2, 17751.9]</t>
+          <t>[20148.6, 17195.1, 19281.6]</t>
         </is>
       </c>
     </row>
@@ -1054,31 +1054,31 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2453.74</v>
+        <v>3136.81</v>
       </c>
       <c r="E18" t="n">
-        <v>2401.37</v>
+        <v>3114.44</v>
       </c>
       <c r="F18" t="n">
-        <v>12.45</v>
+        <v>16.66</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>[17132.17, 15635.62, 17659.12]</t>
+          <t>[14479.56, 16268.49, 15857.23]</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[20242.2, 17751.9, 19636.9]</t>
+          <t>[17195.1, 19281.6, 19471.9]</t>
         </is>
       </c>
     </row>
@@ -1090,31 +1090,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1509.41</v>
+        <v>2689.32</v>
       </c>
       <c r="E19" t="n">
-        <v>1466.99</v>
+        <v>2582.47</v>
       </c>
       <c r="F19" t="n">
-        <v>7.85</v>
+        <v>13.25</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>[15940.87, 18024.69, 18015.68]</t>
+          <t>[16482.98, 16097.54, 18347.07]</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[17751.9, 19636.9, 18993.4]</t>
+          <t>[19281.6, 19471.9, 19921.5]</t>
         </is>
       </c>
     </row>
@@ -1126,31 +1126,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1559.58</v>
+        <v>1935.33</v>
       </c>
       <c r="E20" t="n">
-        <v>1464.03</v>
+        <v>1620.34</v>
       </c>
       <c r="F20" t="n">
-        <v>7.61</v>
+        <v>8.25</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>[18154.34, 18196.76, 16949.21]</t>
+          <t>[16400.08, 18710.83, 19288.07]</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[19636.9, 18993.4, 19062.1]</t>
+          <t>[19471.9, 19921.5, 19866.6]</t>
         </is>
       </c>
     </row>
@@ -1162,31 +1162,31 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2488.42</v>
+        <v>803.72</v>
       </c>
       <c r="E21" t="n">
-        <v>2130.27</v>
+        <v>645.45</v>
       </c>
       <c r="F21" t="n">
-        <v>11.28</v>
+        <v>3.13</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>[18346.68, 17101.39, 14992.1]</t>
+          <t>[19316.88, 19947.01, 19762.36]</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[18993.4, 19062.1, 18775.5]</t>
+          <t>[19921.5, 19866.6, 21013.7]</t>
         </is>
       </c>
     </row>
@@ -1198,31 +1198,31 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>9419.639999999999</v>
+        <v>7168.75</v>
       </c>
       <c r="E22" t="n">
-        <v>9311.91</v>
+        <v>6738.57</v>
       </c>
       <c r="F22" t="n">
-        <v>21.73</v>
+        <v>14.24</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>[32729.41, 30954.36, 37478.8]</t>
+          <t>[39068.38, 40246.51, 39877.51]</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[43730.7, 40363.1, 45004.5]</t>
+          <t>[43050.1, 46554.1, 49803.9]</t>
         </is>
       </c>
     </row>
@@ -1234,31 +1234,31 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>7192.86</v>
+        <v>12782.25</v>
       </c>
       <c r="E23" t="n">
-        <v>7104.95</v>
+        <v>11905.07</v>
       </c>
       <c r="F23" t="n">
-        <v>16.9</v>
+        <v>23.78</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>[31773.83, 39124.56, 34973.67]</t>
+          <t>[39567.83, 39225.84, 33578.62]</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[40363.1, 45004.5, 41819.3]</t>
+          <t>[46554.1, 49803.9, 51729.5]</t>
         </is>
       </c>
     </row>
@@ -1270,31 +1270,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>5526.37</v>
+        <v>10220.54</v>
       </c>
       <c r="E24" t="n">
-        <v>5418.18</v>
+        <v>9304.15</v>
       </c>
       <c r="F24" t="n">
-        <v>12.59</v>
+        <v>18.49</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>[40866.96, 36499.81, 36105.8]</t>
+          <t>[42566.63, 36530.38, 41922.54]</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>[45004.5, 41819.3, 42903.3]</t>
+          <t>[49803.9, 51729.5, 47398.6]</t>
         </is>
       </c>
     </row>
@@ -1306,31 +1306,31 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6593.69</v>
+        <v>9953.610000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>6501</v>
+        <v>8811.969999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>15.02</v>
+        <v>18.27</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>[36682.5, 36372.01, 36769.5]</t>
+          <t>[36381.15, 42158.38, 35663.16]</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>[41819.3, 42903.3, 44604.4]</t>
+          <t>[51729.5, 47398.6, 41510.5]</t>
         </is>
       </c>
     </row>
@@ -1342,31 +1342,31 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6177.14</v>
+        <v>3102.81</v>
       </c>
       <c r="E26" t="n">
-        <v>6037.31</v>
+        <v>3089.85</v>
       </c>
       <c r="F26" t="n">
-        <v>14.22</v>
+        <v>7.33</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>[36652.71, 37083.83, 34327.83]</t>
+          <t>[44641.89, 38061.25, 35856.51]</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[42903.3, 44604.4, 38668.6]</t>
+          <t>[47398.6, 41510.5, 38920.1]</t>
         </is>
       </c>
     </row>
@@ -1378,31 +1378,31 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>6137.25</v>
+        <v>2969.55</v>
       </c>
       <c r="E27" t="n">
-        <v>5961.61</v>
+        <v>2935.06</v>
       </c>
       <c r="F27" t="n">
-        <v>14</v>
+        <v>7.23</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>[37484.83, 34763.08, 36190.35]</t>
+          <t>[38666.27, 36486.66, 44552.22]</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>[44604.4, 38668.6, 43050.1]</t>
+          <t>[41510.5, 38920.1, 41024.7]</t>
         </is>
       </c>
     </row>
@@ -1414,31 +1414,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6059.33</v>
+        <v>3117.3</v>
       </c>
       <c r="E28" t="n">
-        <v>5665.46</v>
+        <v>3043.04</v>
       </c>
       <c r="F28" t="n">
-        <v>12.94</v>
+        <v>7.56</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>[35697.94, 37254.08, 38324.41]</t>
+          <t>[36651.61, 44941.05, 43275.09]</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>[38668.6, 43050.1, 46554.1]</t>
+          <t>[38920.1, 41024.7, 40330.8]</t>
         </is>
       </c>
     </row>
@@ -1450,31 +1450,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>7168.75</v>
+        <v>4774.94</v>
       </c>
       <c r="E29" t="n">
-        <v>6738.57</v>
+        <v>4735.88</v>
       </c>
       <c r="F29" t="n">
-        <v>14.24</v>
+        <v>11.47</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>[39068.38, 40246.51, 39877.51]</t>
+          <t>[46547.01, 44978.97, 46812.66]</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>[43050.1, 46554.1, 49803.9]</t>
+          <t>[41024.7, 40330.8, 42775.5]</t>
         </is>
       </c>
     </row>
@@ -1486,31 +1486,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12782.25</v>
+        <v>5707.16</v>
       </c>
       <c r="E30" t="n">
-        <v>11905.07</v>
+        <v>5301.54</v>
       </c>
       <c r="F30" t="n">
-        <v>23.78</v>
+        <v>13.38</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>[39567.83, 39225.84, 33578.62]</t>
+          <t>[44463.95, 46279.2, 46347.88]</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>[46554.1, 49803.9, 51729.5]</t>
+          <t>[40330.8, 42775.5, 38080.1]</t>
         </is>
       </c>
     </row>
@@ -1522,31 +1522,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10220.54</v>
+        <v>6898.05</v>
       </c>
       <c r="E31" t="n">
-        <v>9304.15</v>
+        <v>6482.85</v>
       </c>
       <c r="F31" t="n">
-        <v>18.49</v>
+        <v>17.54</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>[42566.63, 36530.38, 41922.54]</t>
+          <t>[45935.82, 45991.27, 42615.16]</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>[49803.9, 51729.5, 47398.6]</t>
+          <t>[42775.5, 38080.1, 34238.1]</t>
         </is>
       </c>
     </row>
@@ -1558,31 +1558,31 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1405.58</v>
+        <v>2901.9</v>
       </c>
       <c r="E32" t="n">
-        <v>1404.81</v>
+        <v>2901.84</v>
       </c>
       <c r="F32" t="n">
-        <v>81.48999999999999</v>
+        <v>88.03</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>[317.9, 298.81, 341.37]</t>
+          <t>[399.29, 389.29, 394.78]</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>[1750.4, 1637.7, 1784.4]</t>
+          <t>[3327.4, 3278.0, 3283.5]</t>
         </is>
       </c>
     </row>
@@ -1594,31 +1594,31 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1292.87</v>
+        <v>2781.5</v>
       </c>
       <c r="E33" t="n">
-        <v>1292.77</v>
+        <v>2780.06</v>
       </c>
       <c r="F33" t="n">
-        <v>75.59</v>
+        <v>86.09</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>[363.66, 470.79, 421.74]</t>
+          <t>[427.77, 447.43, 469.82]</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>[1637.7, 1784.4, 1712.4]</t>
+          <t>[3278.0, 3283.5, 3123.7]</t>
         </is>
       </c>
     </row>
@@ -1630,31 +1630,31 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1310.47</v>
+        <v>2825.65</v>
       </c>
       <c r="E34" t="n">
-        <v>1307.1</v>
+        <v>2820.52</v>
       </c>
       <c r="F34" t="n">
-        <v>73.66</v>
+        <v>84.7</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>[536.73, 478.47, 382.89]</t>
+          <t>[473.82, 506.09, 546.84]</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>[1784.4, 1712.4, 1822.6]</t>
+          <t>[3283.5, 3123.7, 3581.1]</t>
         </is>
       </c>
     </row>
@@ -1666,31 +1666,31 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1372.98</v>
+        <v>3341.76</v>
       </c>
       <c r="E35" t="n">
-        <v>1368.62</v>
+        <v>3265.73</v>
       </c>
       <c r="F35" t="n">
-        <v>77.26000000000001</v>
+        <v>84.73999999999999</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>[497.7, 390.82, 314.32]</t>
+          <t>[551.28, 595.62, 550.21]</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>[1712.4, 1822.6, 1773.7]</t>
+          <t>[3123.7, 3581.1, 4789.5]</t>
         </is>
       </c>
     </row>
@@ -1702,31 +1702,31 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1658.57</v>
+        <v>3654.08</v>
       </c>
       <c r="E36" t="n">
-        <v>1632</v>
+        <v>3617.53</v>
       </c>
       <c r="F36" t="n">
-        <v>81.8</v>
+        <v>85.16</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>[413.03, 337.19, 303.98]</t>
+          <t>[639.63, 597.57, 614.21]</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>[1822.6, 1773.7, 2353.9]</t>
+          <t>[3581.1, 4789.5, 4333.4]</t>
         </is>
       </c>
     </row>
@@ -1738,31 +1738,31 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2247.76</v>
+        <v>3917.7</v>
       </c>
       <c r="E37" t="n">
-        <v>2152.62</v>
+        <v>3913.03</v>
       </c>
       <c r="F37" t="n">
-        <v>85.63</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>[348.63, 318.11, 330.39]</t>
+          <t>[661.37, 669.98, 753.75]</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>[1773.7, 2353.9, 3327.4]</t>
+          <t>[4789.5, 4333.4, 4701.3]</t>
         </is>
       </c>
     </row>
@@ -1774,31 +1774,31 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2658.88</v>
+        <v>3699.64</v>
       </c>
       <c r="E38" t="n">
-        <v>2621.41</v>
+        <v>3697.6</v>
       </c>
       <c r="F38" t="n">
-        <v>87.48</v>
+        <v>82.3</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>[360.93, 369.1, 365.02]</t>
+          <t>[746.45, 832.33, 807.22]</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>[2353.9, 3327.4, 3278.0]</t>
+          <t>[4333.4, 4701.3, 4444.1]</t>
         </is>
       </c>
     </row>
@@ -1810,31 +1810,31 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2901.9</v>
+        <v>3590.19</v>
       </c>
       <c r="E39" t="n">
-        <v>2901.84</v>
+        <v>3588.75</v>
       </c>
       <c r="F39" t="n">
-        <v>88.03</v>
+        <v>79.2</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>[399.29, 389.29, 394.78]</t>
+          <t>[971.35, 950.2, 905.3]</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>[3327.4, 3278.0, 3283.5]</t>
+          <t>[4701.3, 4444.1, 4447.7]</t>
         </is>
       </c>
     </row>
@@ -1846,31 +1846,31 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2781.5</v>
+        <v>2808.24</v>
       </c>
       <c r="E40" t="n">
-        <v>2780.06</v>
+        <v>2807.68</v>
       </c>
       <c r="F40" t="n">
-        <v>86.09</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>[427.77, 447.43, 469.82]</t>
+          <t>[1663.38, 1562.12, 1326.56]</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>[3278.0, 3283.5, 3123.7]</t>
+          <t>[4444.1, 4447.7, 4083.3]</t>
         </is>
       </c>
     </row>
@@ -1882,31 +1882,31 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2825.65</v>
+        <v>2498.49</v>
       </c>
       <c r="E41" t="n">
-        <v>2820.52</v>
+        <v>2495.12</v>
       </c>
       <c r="F41" t="n">
-        <v>84.7</v>
+        <v>60.32</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>[473.82, 506.09, 546.84]</t>
+          <t>[1815.33, 1551.58, 1561.82]</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>[3283.5, 3123.7, 3581.1]</t>
+          <t>[4447.7, 4083.3, 3883.1]</t>
         </is>
       </c>
     </row>
@@ -1918,31 +1918,31 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>890.5700000000001</v>
+        <v>887.71</v>
       </c>
       <c r="E42" t="n">
-        <v>882.77</v>
+        <v>887.4299999999999</v>
       </c>
       <c r="F42" t="n">
-        <v>25.64</v>
+        <v>16.57</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>[2122.6, 2248.19, 3447.29]</t>
+          <t>[4997.28, 4730.16, 3808.17]</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>[2905.2, 3066.1, 4495.1]</t>
+          <t>[5916.0, 5600.6, 4681.3]</t>
         </is>
       </c>
     </row>
@@ -1954,31 +1954,31 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1096.69</v>
+        <v>836.8099999999999</v>
       </c>
       <c r="E43" t="n">
-        <v>1035.68</v>
+        <v>829.05</v>
       </c>
       <c r="F43" t="n">
-        <v>23.71</v>
+        <v>17.31</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>[2343.75, 3651.32, 3806.99]</t>
+          <t>[4865.0, 3918.81, 3405.13]</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>[3066.1, 4495.1, 5347.9]</t>
+          <t>[5600.6, 4681.3, 4394.2]</t>
         </is>
       </c>
     </row>
@@ -1990,31 +1990,31 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1332.26</v>
+        <v>799.58</v>
       </c>
       <c r="E44" t="n">
-        <v>1256.67</v>
+        <v>784.84</v>
       </c>
       <c r="F44" t="n">
-        <v>22.15</v>
+        <v>17.34</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>[3829.58, 3972.99, 4940.61]</t>
+          <t>[4098.83, 3573.99, 3601.27]</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>[4495.1, 5347.9, 6670.2]</t>
+          <t>[4681.3, 4394.2, 4553.1]</t>
         </is>
       </c>
     </row>
@@ -2026,31 +2026,31 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1576.31</v>
+        <v>621.86</v>
       </c>
       <c r="E45" t="n">
-        <v>1568.97</v>
+        <v>568.11</v>
       </c>
       <c r="F45" t="n">
-        <v>24.36</v>
+        <v>14.43</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>[3993.87, 4993.1, 5729.82]</t>
+          <t>[3707.9, 3751.76, 2370.99]</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>[5347.9, 6670.2, 7405.6]</t>
+          <t>[4394.2, 4553.1, 2154.3]</t>
         </is>
       </c>
     </row>
@@ -2062,31 +2062,31 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1511.54</v>
+        <v>443.76</v>
       </c>
       <c r="E46" t="n">
-        <v>1509.12</v>
+        <v>381.46</v>
       </c>
       <c r="F46" t="n">
-        <v>22.52</v>
+        <v>11.45</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>[5078.48, 5861.41, 4696.84]</t>
+          <t>[3862.24, 2453.98, 2766.96]</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>[6670.2, 7405.6, 6088.3]</t>
+          <t>[4553.1, 2154.3, 2920.8]</t>
         </is>
       </c>
     </row>
@@ -2098,31 +2098,31 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1344.46</v>
+        <v>379.34</v>
       </c>
       <c r="E47" t="n">
-        <v>1337.67</v>
+        <v>316.27</v>
       </c>
       <c r="F47" t="n">
-        <v>20.94</v>
+        <v>11.12</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>[6100.34, 4897.28, 4399.28]</t>
+          <t>[2545.46, 2890.19, 4248.03]</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>[7405.6, 6088.3, 5916.0]</t>
+          <t>[2154.3, 2920.8, 3721.0]</t>
         </is>
       </c>
     </row>
@@ -2134,31 +2134,31 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1134.62</v>
+        <v>275.17</v>
       </c>
       <c r="E48" t="n">
-        <v>1124.32</v>
+        <v>208.72</v>
       </c>
       <c r="F48" t="n">
-        <v>19.24</v>
+        <v>5.6</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>[5175.07, 4647.91, 4408.95]</t>
+          <t>[2858.75, 4182.21, 4628.2]</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>[6088.3, 5916.0, 5600.6]</t>
+          <t>[2920.8, 3721.0, 4525.3]</t>
         </is>
       </c>
     </row>
@@ -2170,31 +2170,31 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>887.71</v>
+        <v>351.76</v>
       </c>
       <c r="E49" t="n">
-        <v>887.4299999999999</v>
+        <v>298.43</v>
       </c>
       <c r="F49" t="n">
-        <v>16.57</v>
+        <v>7.24</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>[4997.28, 4730.16, 3808.17]</t>
+          <t>[4277.57, 4739.81, 6252.31]</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>[5916.0, 5600.6, 4681.3]</t>
+          <t>[3721.0, 4525.3, 6128.1]</t>
         </is>
       </c>
     </row>
@@ -2206,31 +2206,31 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>836.8099999999999</v>
+        <v>360.32</v>
       </c>
       <c r="E50" t="n">
-        <v>829.05</v>
+        <v>304.17</v>
       </c>
       <c r="F50" t="n">
-        <v>17.31</v>
+        <v>5.3</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>[4865.0, 3918.81, 3405.13]</t>
+          <t>[4739.75, 6253.68, 6863.38]</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>[5600.6, 4681.3, 4394.2]</t>
+          <t>[4525.3, 6128.1, 6290.9]</t>
         </is>
       </c>
     </row>
@@ -2242,31 +2242,31 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>799.58</v>
+        <v>403.9</v>
       </c>
       <c r="E51" t="n">
-        <v>784.84</v>
+        <v>356.79</v>
       </c>
       <c r="F51" t="n">
-        <v>17.34</v>
+        <v>5.75</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>[4098.83, 3573.99, 3601.27]</t>
+          <t>[6286.0, 6902.35, 5775.37]</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>[4681.3, 4394.2, 4553.1]</t>
+          <t>[6128.1, 6290.9, 6076.4]</t>
         </is>
       </c>
     </row>
@@ -2278,31 +2278,31 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>30.06</v>
+        <v>2.94</v>
       </c>
       <c r="E52" t="n">
-        <v>21.24</v>
+        <v>2.92</v>
       </c>
       <c r="F52" t="n">
-        <v>124.01</v>
+        <v>18.88</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>[68.32, 26.2, 19.89]</t>
+          <t>[12.35, 12.52, 17.53]</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>[17.2, 16.9, 16.6]</t>
+          <t>[15.7, 15.5, 15.1]</t>
         </is>
       </c>
     </row>
@@ -2314,31 +2314,31 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>5.47</v>
+        <v>3.1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.49</v>
+        <v>3.06</v>
       </c>
       <c r="F53" t="n">
-        <v>26.83</v>
+        <v>20.19</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>[25.8, 18.7, 18.66]</t>
+          <t>[12.64, 17.73, 18.71]</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>[16.9, 16.6, 16.2]</t>
+          <t>[15.5, 15.1, 15.0]</t>
         </is>
       </c>
     </row>
@@ -2350,31 +2350,31 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1.41</v>
+        <v>2.59</v>
       </c>
       <c r="E54" t="n">
-        <v>1.17</v>
+        <v>2.18</v>
       </c>
       <c r="F54" t="n">
-        <v>7.16</v>
+        <v>14.51</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>[18.05, 18.16, 16.21]</t>
+          <t>[17.66, 18.66, 15.43]</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>[16.6, 16.2, 16.1]</t>
+          <t>[15.1, 15.0, 15.1]</t>
         </is>
       </c>
     </row>
@@ -2386,31 +2386,31 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.35</v>
+        <v>19.16</v>
       </c>
       <c r="E55" t="n">
-        <v>7.14</v>
+        <v>12.25</v>
       </c>
       <c r="F55" t="n">
-        <v>45.07</v>
+        <v>82.14</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>[17.94, 16.02, 35.38]</t>
+          <t>[18.53, 15.32, 47.89]</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>[16.2, 16.1, 15.8]</t>
+          <t>[15.0, 15.1, 14.9]</t>
         </is>
       </c>
     </row>
@@ -2422,31 +2422,31 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.5</v>
+        <v>19.13</v>
       </c>
       <c r="E56" t="n">
-        <v>7.73</v>
+        <v>12.56</v>
       </c>
       <c r="F56" t="n">
-        <v>48.94</v>
+        <v>84.29000000000001</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>[15.87, 35.43, 12.46]</t>
+          <t>[15.28, 47.69, 19.61]</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>[16.1, 15.8, 15.8]</t>
+          <t>[15.1, 14.9, 14.9]</t>
         </is>
       </c>
     </row>
@@ -2458,31 +2458,31 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.68</v>
+        <v>18.82</v>
       </c>
       <c r="E57" t="n">
-        <v>8.74</v>
+        <v>12.66</v>
       </c>
       <c r="F57" t="n">
-        <v>55.33</v>
+        <v>85.02</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>[35.5, 12.59, 12.4]</t>
+          <t>[47.17, 19.35, 15.98]</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>[15.8, 15.8, 15.7]</t>
+          <t>[14.9, 14.9, 14.7]</t>
         </is>
       </c>
     </row>
@@ -2494,31 +2494,31 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>3.23</v>
+        <v>2.34</v>
       </c>
       <c r="E58" t="n">
-        <v>3.22</v>
+        <v>1.81</v>
       </c>
       <c r="F58" t="n">
-        <v>20.56</v>
+        <v>12.24</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>[12.56, 12.31, 12.47]</t>
+          <t>[18.78, 15.24, 15.51]</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>[15.8, 15.7, 15.5]</t>
+          <t>[14.9, 14.7, 14.5]</t>
         </is>
       </c>
     </row>
@@ -2530,31 +2530,31 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2.94</v>
+        <v>0.55</v>
       </c>
       <c r="E59" t="n">
-        <v>2.92</v>
+        <v>0.52</v>
       </c>
       <c r="F59" t="n">
-        <v>18.88</v>
+        <v>3.59</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>[12.35, 12.52, 17.53]</t>
+          <t>[14.96, 15.19, 13.68]</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>[15.7, 15.5, 15.1]</t>
+          <t>[14.7, 14.5, 14.3]</t>
         </is>
       </c>
     </row>
@@ -2566,31 +2566,31 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.1</v>
+        <v>6.03</v>
       </c>
       <c r="E60" t="n">
-        <v>3.06</v>
+        <v>3.9</v>
       </c>
       <c r="F60" t="n">
-        <v>20.19</v>
+        <v>27.42</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>[12.64, 17.73, 18.71]</t>
+          <t>[15.04, 13.54, 24.6]</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>[15.5, 15.1, 15.0]</t>
+          <t>[14.5, 14.3, 14.2]</t>
         </is>
       </c>
     </row>
@@ -2602,31 +2602,31 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2.59</v>
+        <v>6.26</v>
       </c>
       <c r="E61" t="n">
-        <v>2.18</v>
+        <v>4.7</v>
       </c>
       <c r="F61" t="n">
-        <v>14.51</v>
+        <v>33.21</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>[17.66, 18.66, 15.43]</t>
+          <t>[13.52, 24.61, 11.09]</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>[15.1, 15.0, 15.1]</t>
+          <t>[14.3, 14.2, 14.0]</t>
         </is>
       </c>
     </row>
@@ -2638,31 +2638,31 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.17</v>
+        <v>0.06</v>
       </c>
       <c r="E62" t="n">
-        <v>0.17</v>
+        <v>0.06</v>
       </c>
       <c r="F62" t="n">
-        <v>86.95999999999999</v>
+        <v>61.76</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>[0.03, 0.03, 0.02]</t>
+          <t>[0.04, 0.04, 0.03]</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>[0.2, 0.2, 0.2]</t>
+          <t>[0.1, 0.1, 0.1]</t>
         </is>
       </c>
     </row>
@@ -2674,31 +2674,31 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.17</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E63" t="n">
-        <v>0.17</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F63" t="n">
-        <v>83</v>
+        <v>67.83</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>[0.03, 0.02, 0.05]</t>
+          <t>[0.04, 0.03, 0.03]</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>[0.2, 0.2, 0.2]</t>
+          <t>[0.1, 0.1, 0.1]</t>
         </is>
       </c>
     </row>
@@ -2710,31 +2710,31 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="E64" t="n">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="F64" t="n">
-        <v>78.84</v>
+        <v>76.56999999999999</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>[0.03, 0.05, 0.05]</t>
+          <t>[0.03, 0.03, 0.01]</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>[0.2, 0.2, 0.2]</t>
+          <t>[0.1, 0.1, 0.1]</t>
         </is>
       </c>
     </row>
@@ -2746,31 +2746,31 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="E65" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="F65" t="n">
-        <v>73.28</v>
+        <v>83.16</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>[0.06, 0.05, 0.05]</t>
+          <t>[0.03, 0.01, 0.03]</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>[0.2, 0.2, 0.2]</t>
+          <t>[0.1, 0.1, 0.2]</t>
         </is>
       </c>
     </row>
@@ -2782,31 +2782,31 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="E66" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="F66" t="n">
-        <v>80.12</v>
+        <v>83.7</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>[0.05, 0.06, 0.01]</t>
+          <t>[0.01, 0.03, 0.03]</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>[0.2, 0.2, 0.2]</t>
+          <t>[0.1, 0.2, 0.1]</t>
         </is>
       </c>
     </row>
@@ -2818,31 +2818,31 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="E67" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="F67" t="n">
-        <v>76.23999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>[0.06, 0.01, 0.04]</t>
+          <t>[0.03, 0.03, 0.03]</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>[0.2, 0.2, 0.1]</t>
+          <t>[0.2, 0.1, 0.1]</t>
         </is>
       </c>
     </row>
@@ -2854,31 +2854,31 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="E68" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="F68" t="n">
-        <v>73.70999999999999</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>[0.01, 0.04, 0.03]</t>
+          <t>[0.03, 0.03, 0.06]</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>[0.2, 0.1, 0.1]</t>
+          <t>[0.1, 0.1, 0.3]</t>
         </is>
       </c>
     </row>
@@ -2890,31 +2890,31 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
       <c r="E69" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="F69" t="n">
-        <v>61.76</v>
+        <v>61.04</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>[0.04, 0.04, 0.03]</t>
+          <t>[0.03, 0.07, 0.06]</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>[0.1, 0.1, 0.1]</t>
+          <t>[0.1, 0.3, 0.1]</t>
         </is>
       </c>
     </row>
@@ -2926,31 +2926,31 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="E70" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="F70" t="n">
-        <v>67.83</v>
+        <v>69.86</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>[0.04, 0.03, 0.03]</t>
+          <t>[0.06, 0.05, 0.05]</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>[0.1, 0.1, 0.1]</t>
+          <t>[0.3, 0.1, 0.3]</t>
         </is>
       </c>
     </row>
@@ -2962,31 +2962,31 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.08</v>
+        <v>0.18</v>
       </c>
       <c r="E71" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="F71" t="n">
-        <v>76.56999999999999</v>
+        <v>72.87</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>[0.03, 0.03, 0.01]</t>
+          <t>[0.06, 0.06, 0.01]</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>[0.1, 0.1, 0.1]</t>
+          <t>[0.1, 0.3, 0.2]</t>
         </is>
       </c>
     </row>
@@ -2998,31 +2998,31 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1703.98</v>
+        <v>684.0700000000001</v>
       </c>
       <c r="E72" t="n">
-        <v>1534.27</v>
+        <v>614.05</v>
       </c>
       <c r="F72" t="n">
-        <v>10.93</v>
+        <v>4.12</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>[16470.3, 14908.52, 15562.87]</t>
+          <t>[15602.01, 14938.86, 15494.81]</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>[14208.6, 14391.8, 13738.5]</t>
+          <t>[14567.7, 14597.2, 15961.0]</t>
         </is>
       </c>
     </row>
@@ -3034,31 +3034,31 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1064.62</v>
+        <v>754.14</v>
       </c>
       <c r="E73" t="n">
-        <v>940.25</v>
+        <v>653.45</v>
       </c>
       <c r="F73" t="n">
-        <v>6.77</v>
+        <v>3.94</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>[14705.5, 15274.14, 14929.81]</t>
+          <t>[14897.79, 15476.41, 16320.43]</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>[14391.8, 13738.5, 13958.4]</t>
+          <t>[14597.2, 15961.0, 17495.6]</t>
         </is>
       </c>
     </row>
@@ -3070,31 +3070,31 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>823.84</v>
+        <v>840.05</v>
       </c>
       <c r="E74" t="n">
-        <v>722.16</v>
+        <v>702.16</v>
       </c>
       <c r="F74" t="n">
-        <v>5.15</v>
+        <v>4.13</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>[14970.7, 14627.27, 15899.51]</t>
+          <t>[15352.67, 16187.61, 17456.25]</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>[13738.5, 13958.4, 15634.1]</t>
+          <t>[15961.0, 17495.6, 17266.1]</t>
         </is>
       </c>
     </row>
@@ -3106,31 +3106,31 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>486.3</v>
+        <v>931.35</v>
       </c>
       <c r="E75" t="n">
-        <v>365.28</v>
+        <v>824.3099999999999</v>
       </c>
       <c r="F75" t="n">
-        <v>2.54</v>
+        <v>4.88</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>[14742.21, 15942.48, 14536.54]</t>
+          <t>[16182.07, 17525.84, 16892.68]</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>[13958.4, 15634.1, 14532.9]</t>
+          <t>[17495.6, 17266.1, 15993.0]</t>
         </is>
       </c>
     </row>
@@ -3142,31 +3142,31 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>739.36</v>
+        <v>754.95</v>
       </c>
       <c r="E76" t="n">
-        <v>523.33</v>
+        <v>716.73</v>
       </c>
       <c r="F76" t="n">
-        <v>3.72</v>
+        <v>4.46</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>[15868.3, 14453.61, 15049.92]</t>
+          <t>[17704.56, 17011.03, 16202.3]</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>[15634.1, 14532.9, 13793.4]</t>
+          <t>[17266.1, 15993.0, 15508.6]</t>
         </is>
       </c>
     </row>
@@ -3178,31 +3178,31 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>991.58</v>
+        <v>1644.75</v>
       </c>
       <c r="E77" t="n">
-        <v>810.11</v>
+        <v>1353.99</v>
       </c>
       <c r="F77" t="n">
-        <v>5.73</v>
+        <v>7.62</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>[14527.24, 15076.91, 15708.88]</t>
+          <t>[16863.83, 16039.84, 16350.1]</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>[14532.9, 13793.4, 14567.7]</t>
+          <t>[15993.0, 15508.6, 19010.0]</t>
         </is>
       </c>
     </row>
@@ -3214,31 +3214,31 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1009.33</v>
+        <v>2350.68</v>
       </c>
       <c r="E78" t="n">
-        <v>932.6900000000001</v>
+        <v>2029.19</v>
       </c>
       <c r="F78" t="n">
-        <v>6.56</v>
+        <v>11</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>[15063.91, 15702.51, 14989.95]</t>
+          <t>[15860.11, 16176.12, 15443.52]</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>[13793.4, 14567.7, 14597.2]</t>
+          <t>[15508.6, 19010.0, 18345.7]</t>
         </is>
       </c>
     </row>
@@ -3250,31 +3250,31 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>684.0700000000001</v>
+        <v>3139.31</v>
       </c>
       <c r="E79" t="n">
-        <v>614.05</v>
+        <v>3128.18</v>
       </c>
       <c r="F79" t="n">
-        <v>4.12</v>
+        <v>16.22</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>[15602.01, 14938.86, 15494.81]</t>
+          <t>[16105.2, 15365.0, 16924.85]</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>[14567.7, 14597.2, 15961.0]</t>
+          <t>[19010.0, 18345.7, 20423.9]</t>
         </is>
       </c>
     </row>
@@ -3286,31 +3286,31 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>754.14</v>
+        <v>3762.32</v>
       </c>
       <c r="E80" t="n">
-        <v>653.45</v>
+        <v>3563.51</v>
       </c>
       <c r="F80" t="n">
-        <v>3.94</v>
+        <v>17.71</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>[14897.79, 15476.41, 16320.43]</t>
+          <t>[15843.55, 17487.23, 15664.61]</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>[14597.2, 15961.0, 17495.6]</t>
+          <t>[18345.7, 20423.9, 20916.3]</t>
         </is>
       </c>
     </row>
@@ -3322,31 +3322,31 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>840.05</v>
+        <v>4564.63</v>
       </c>
       <c r="E81" t="n">
-        <v>702.16</v>
+        <v>4401.82</v>
       </c>
       <c r="F81" t="n">
-        <v>4.13</v>
+        <v>20.78</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>[15352.67, 16187.61, 17456.25]</t>
+          <t>[17713.86, 15876.63, 16376.27]</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>[15961.0, 17495.6, 17266.1]</t>
+          <t>[20423.9, 20916.3, 21832.0]</t>
         </is>
       </c>
     </row>
@@ -3358,31 +3358,31 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1034.1</v>
+        <v>1152.65</v>
       </c>
       <c r="E82" t="n">
-        <v>937</v>
+        <v>1139.92</v>
       </c>
       <c r="F82" t="n">
-        <v>12.28</v>
+        <v>10.6</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>[6871.94, 6086.49, 8881.74]</t>
+          <t>[15769.05, 12559.65, 9532.05]</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>[8077.7, 6406.5, 7596.5]</t>
+          <t>[14534.9, 11659.5, 8246.6]</t>
         </is>
       </c>
     </row>
@@ -3394,31 +3394,31 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1179.52</v>
+        <v>1235.73</v>
       </c>
       <c r="E83" t="n">
-        <v>1023.53</v>
+        <v>1202.47</v>
       </c>
       <c r="F83" t="n">
-        <v>12.99</v>
+        <v>14.56</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>[6202.54, 9138.04, 9873.6]</t>
+          <t>[12499.69, 9477.85, 8662.97]</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>[6406.5, 7596.5, 8548.5]</t>
+          <t>[11659.5, 8246.6, 7127.0]</t>
         </is>
       </c>
     </row>
@@ -3430,31 +3430,31 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1457.78</v>
+        <v>1550.17</v>
       </c>
       <c r="E84" t="n">
-        <v>1454.03</v>
+        <v>1522.63</v>
       </c>
       <c r="F84" t="n">
-        <v>16.52</v>
+        <v>20.77</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>[9194.7, 9958.88, 9913.3]</t>
+          <t>[9431.25, 8615.48, 8895.25]</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>[7596.5, 8548.5, 11266.8]</t>
+          <t>[8246.6, 7127.0, 7000.5]</t>
         </is>
       </c>
     </row>
@@ -3466,31 +3466,31 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1441.03</v>
+        <v>1983.57</v>
       </c>
       <c r="E85" t="n">
-        <v>1437.06</v>
+        <v>1934.12</v>
       </c>
       <c r="F85" t="n">
-        <v>12.94</v>
+        <v>33.69</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>[9834.69, 9745.76, 13114.47]</t>
+          <t>[8578.61, 8835.34, 7133.81]</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>[8548.5, 11266.8, 14618.4]</t>
+          <t>[7127.0, 7000.5, 4617.9]</t>
         </is>
       </c>
     </row>
@@ -3502,31 +3502,31 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>2175.59</v>
+        <v>2145.6</v>
       </c>
       <c r="E86" t="n">
-        <v>2092.15</v>
+        <v>2128.2</v>
       </c>
       <c r="F86" t="n">
-        <v>14.03</v>
+        <v>43.39</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>[9614.39, 12930.17, 15568.5]</t>
+          <t>[8765.74, 7040.43, 6381.22]</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>[11266.8, 14618.4, 18504.3]</t>
+          <t>[7000.5, 4617.9, 4184.4]</t>
         </is>
       </c>
     </row>
@@ -3538,31 +3538,31 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1844.16</v>
+        <v>2097.19</v>
       </c>
       <c r="E87" t="n">
-        <v>1700.24</v>
+        <v>2083.46</v>
       </c>
       <c r="F87" t="n">
-        <v>10.37</v>
+        <v>43.33</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>[13130.55, 15842.69, 15486.17]</t>
+          <t>[6968.25, 6315.12, 8047.31]</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>[14618.4, 18504.3, 14534.9]</t>
+          <t>[4617.9, 4184.4, 6278.0]</t>
         </is>
       </c>
     </row>
@@ -3574,31 +3574,31 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1680.3</v>
+        <v>1765.88</v>
       </c>
       <c r="E88" t="n">
-        <v>1454.69</v>
+        <v>1755.51</v>
       </c>
       <c r="F88" t="n">
-        <v>9.119999999999999</v>
+        <v>32.58</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>[15871.73, 15543.48, 12382.44]</t>
+          <t>[6148.09, 7780.13, 8496.7]</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>[18504.3, 14534.9, 11659.5]</t>
+          <t>[4184.4, 6278.0, 6696.0]</t>
         </is>
       </c>
     </row>
@@ -3610,31 +3610,31 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1152.65</v>
+        <v>1344</v>
       </c>
       <c r="E89" t="n">
-        <v>1139.92</v>
+        <v>1336.68</v>
       </c>
       <c r="F89" t="n">
-        <v>10.6</v>
+        <v>20.02</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>[15769.05, 12559.65, 9532.05]</t>
+          <t>[7426.81, 8072.24, 8484.19]</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>[14534.9, 11659.5, 8246.6]</t>
+          <t>[6278.0, 6696.0, 6999.2]</t>
         </is>
       </c>
     </row>
@@ -3646,31 +3646,31 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1235.73</v>
+        <v>1001.44</v>
       </c>
       <c r="E90" t="n">
-        <v>1202.47</v>
+        <v>831.01</v>
       </c>
       <c r="F90" t="n">
-        <v>14.56</v>
+        <v>12.06</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>[12499.69, 9477.85, 8662.97]</t>
+          <t>[7872.52, 8273.03, 10733.18]</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>[11659.5, 8246.6, 7127.0]</t>
+          <t>[6696.0, 6999.2, 10690.5]</t>
         </is>
       </c>
     </row>
@@ -3682,31 +3682,31 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1550.17</v>
+        <v>1077.05</v>
       </c>
       <c r="E91" t="n">
-        <v>1522.63</v>
+        <v>939.25</v>
       </c>
       <c r="F91" t="n">
-        <v>20.77</v>
+        <v>9.48</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>[9431.25, 8615.48, 8895.25]</t>
+          <t>[8066.58, 10451.31, 12298.83]</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>[8246.6, 7127.0, 7000.5]</t>
+          <t>[6999.2, 10690.5, 13810.0]</t>
         </is>
       </c>
     </row>
@@ -3718,31 +3718,31 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1129.93</v>
+        <v>1417.29</v>
       </c>
       <c r="E92" t="n">
-        <v>895.3200000000001</v>
+        <v>1406.98</v>
       </c>
       <c r="F92" t="n">
-        <v>7.48</v>
+        <v>11.39</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>[10079.83, 10158.47, 11095.09]</t>
+          <t>[11642.91, 11517.76, 9688.97]</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>[9718.4, 10614.4, 12963.7]</t>
+          <t>[12949.8, 13164.9, 10955.9]</t>
         </is>
       </c>
     </row>
@@ -3754,31 +3754,31 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1217.97</v>
+        <v>1439.16</v>
       </c>
       <c r="E93" t="n">
-        <v>997.01</v>
+        <v>1427.62</v>
       </c>
       <c r="F93" t="n">
-        <v>8.029999999999999</v>
+        <v>11.96</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>[10081.86, 10977.94, 12144.58]</t>
+          <t>[11620.05, 9785.19, 10069.31]</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>[10614.4, 12963.7, 12617.3]</t>
+          <t>[13164.9, 10955.9, 11636.6]</t>
         </is>
       </c>
     </row>
@@ -3790,31 +3790,31 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1162.72</v>
+        <v>1302.07</v>
       </c>
       <c r="E94" t="n">
-        <v>929.22</v>
+        <v>1292.81</v>
       </c>
       <c r="F94" t="n">
-        <v>7.25</v>
+        <v>11.69</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>[11046.39, 12203.46, 12823.22]</t>
+          <t>[9845.83, 10147.69, 9250.54]</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>[12963.7, 12617.3, 12366.7]</t>
+          <t>[10955.9, 11636.6, 10530.0]</t>
         </is>
       </c>
     </row>
@@ -3826,31 +3826,31 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>868.49</v>
+        <v>1085.5</v>
       </c>
       <c r="E95" t="n">
-        <v>748.36</v>
+        <v>962.3</v>
       </c>
       <c r="F95" t="n">
-        <v>5.85</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>[12366.95, 13039.52, 14390.11]</t>
+          <t>[10213.95, 9329.36, 8499.8]</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>[12617.3, 12366.7, 13068.2]</t>
+          <t>[11636.6, 10530.0, 8763.4]</t>
         </is>
       </c>
     </row>
@@ -3862,31 +3862,31 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>911.37</v>
+        <v>831.79</v>
       </c>
       <c r="E96" t="n">
-        <v>713.1</v>
+        <v>722.73</v>
       </c>
       <c r="F96" t="n">
-        <v>5.57</v>
+        <v>7.01</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>[13097.12, 14467.56, 11671.53]</t>
+          <t>[9389.38, 8600.82, 9494.51]</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>[12366.7, 13068.2, 11662.0]</t>
+          <t>[10530.0, 8763.4, 10359.5]</t>
         </is>
       </c>
     </row>
@@ -3898,31 +3898,31 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1021.97</v>
+        <v>445.9</v>
       </c>
       <c r="E97" t="n">
-        <v>860.15</v>
+        <v>294.84</v>
       </c>
       <c r="F97" t="n">
-        <v>6.64</v>
+        <v>2.89</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>[14327.1, 11582.25, 11708.0]</t>
+          <t>[8682.67, 9592.29, 10422.63]</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>[13068.2, 11662.0, 12949.8]</t>
+          <t>[8763.4, 10359.5, 10459.2]</t>
         </is>
       </c>
     </row>
@@ -3934,31 +3934,31 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1237.88</v>
+        <v>441.74</v>
       </c>
       <c r="E98" t="n">
-        <v>1053.64</v>
+        <v>306.16</v>
       </c>
       <c r="F98" t="n">
-        <v>8.109999999999999</v>
+        <v>2.92</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>[11506.01, 11617.51, 11492.26]</t>
+          <t>[9609.13, 10439.21, 11284.62]</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>[11662.0, 12949.8, 13164.9]</t>
+          <t>[10359.5, 10459.2, 11136.5]</t>
         </is>
       </c>
     </row>
@@ -3970,31 +3970,31 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1417.29</v>
+        <v>822.34</v>
       </c>
       <c r="E99" t="n">
-        <v>1406.98</v>
+        <v>577.87</v>
       </c>
       <c r="F99" t="n">
-        <v>11.39</v>
+        <v>5.45</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>[11642.91, 11517.76, 9688.97]</t>
+          <t>[10532.91, 11398.28, 11907.12]</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>[12949.8, 13164.9, 10955.9]</t>
+          <t>[10459.2, 11136.5, 10509.0]</t>
         </is>
       </c>
     </row>
@@ -4006,31 +4006,31 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1439.16</v>
+        <v>867.02</v>
       </c>
       <c r="E100" t="n">
-        <v>1427.62</v>
+        <v>673.4299999999999</v>
       </c>
       <c r="F100" t="n">
-        <v>11.96</v>
+        <v>6.19</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>[11620.05, 9785.19, 10069.31]</t>
+          <t>[11436.22, 11954.58, 12762.61]</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>[13164.9, 10955.9, 11636.6]</t>
+          <t>[11136.5, 10509.0, 13037.6]</t>
         </is>
       </c>
     </row>
@@ -4042,31 +4042,31 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1302.07</v>
+        <v>882.6900000000001</v>
       </c>
       <c r="E101" t="n">
-        <v>1292.81</v>
+        <v>723.64</v>
       </c>
       <c r="F101" t="n">
-        <v>11.69</v>
+        <v>6.61</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>[9845.83, 10147.69, 9250.54]</t>
+          <t>[11941.47, 12748.28, 10796.65]</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>[10955.9, 11636.6, 10530.0]</t>
+          <t>[10509.0, 13037.6, 11245.8]</t>
         </is>
       </c>
     </row>
@@ -4078,31 +4078,31 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1023.38</v>
+        <v>5560.48</v>
       </c>
       <c r="E102" t="n">
-        <v>945.85</v>
+        <v>5554.32</v>
       </c>
       <c r="F102" t="n">
-        <v>1.76</v>
+        <v>11.04</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>[53782.17, 50676.9, 57749.08]</t>
+          <t>[59490.17, 54271.2, 54422.07]</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>[53229.8, 52155.5, 56942.5]</t>
+          <t>[54175.0, 48842.0, 48503.5]</t>
         </is>
       </c>
     </row>
@@ -4114,31 +4114,31 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>2250.83</v>
+        <v>6072.26</v>
       </c>
       <c r="E103" t="n">
-        <v>1916.36</v>
+        <v>5982.95</v>
       </c>
       <c r="F103" t="n">
-        <v>3.61</v>
+        <v>12.47</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>[50797.3, 57775.19, 56206.28]</t>
+          <t>[53877.81, 53989.44, 54422.22]</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>[52155.5, 56942.5, 52648.1]</t>
+          <t>[48842.0, 48503.5, 46995.1]</t>
         </is>
       </c>
     </row>
@@ -4150,31 +4150,31 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>4065.51</v>
+        <v>5137.22</v>
       </c>
       <c r="E104" t="n">
-        <v>3570.69</v>
+        <v>5003.15</v>
       </c>
       <c r="F104" t="n">
-        <v>6.68</v>
+        <v>10.33</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>[58022.95, 56455.49, 59182.63]</t>
+          <t>[53191.04, 53557.68, 54847.94]</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>[56942.5, 52648.1, 53358.4]</t>
+          <t>[48503.5, 46995.1, 51088.6]</t>
         </is>
       </c>
     </row>
@@ -4186,31 +4186,31 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>5887.79</v>
+        <v>4119.71</v>
       </c>
       <c r="E105" t="n">
-        <v>5670.54</v>
+        <v>3869.51</v>
       </c>
       <c r="F105" t="n">
-        <v>10.69</v>
+        <v>7.93</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>[56354.32, 59076.93, 60647.17]</t>
+          <t>[52863.28, 54007.74, 47779.9]</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>[52648.1, 53358.4, 53060.3]</t>
+          <t>[46995.1, 51088.6, 50601.1]</t>
         </is>
       </c>
     </row>
@@ -4222,31 +4222,31 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>7231.82</v>
+        <v>2559.85</v>
       </c>
       <c r="E106" t="n">
-        <v>7109.5</v>
+        <v>2346.03</v>
       </c>
       <c r="F106" t="n">
-        <v>13.28</v>
+        <v>4.8</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>[58779.02, 60312.71, 62693.98]</t>
+          <t>[53126.36, 46875.29, 43180.13]</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>[53358.4, 53060.3, 54038.5]</t>
+          <t>[51088.6, 50601.1, 41905.6]</t>
         </is>
       </c>
     </row>
@@ -4258,31 +4258,31 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>7265.05</v>
+        <v>2758.4</v>
       </c>
       <c r="E107" t="n">
-        <v>7213.3</v>
+        <v>2383.97</v>
       </c>
       <c r="F107" t="n">
-        <v>13.4</v>
+        <v>4.94</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>[59144.14, 61407.88, 62361.68]</t>
+          <t>[46439.68, 42680.64, 49032.35]</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>[53060.3, 54038.5, 54175.0]</t>
+          <t>[50601.1, 41905.6, 46816.9]</t>
         </is>
       </c>
     </row>
@@ -4294,31 +4294,31 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>6401.64</v>
+        <v>4198.7</v>
       </c>
       <c r="E108" t="n">
-        <v>6392.6</v>
+        <v>3571.62</v>
       </c>
       <c r="F108" t="n">
-        <v>12.26</v>
+        <v>7.09</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>[59952.0, 60769.03, 55512.27]</t>
+          <t>[43184.48, 49700.1, 47820.62]</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>[54038.5, 54175.0, 48842.0]</t>
+          <t>[41905.6, 46816.9, 54373.4]</t>
         </is>
       </c>
     </row>
@@ -4330,31 +4330,31 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>5560.48</v>
+        <v>5155.51</v>
       </c>
       <c r="E109" t="n">
-        <v>5554.32</v>
+        <v>4821.99</v>
       </c>
       <c r="F109" t="n">
-        <v>11.04</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>[59490.17, 54271.2, 54422.07]</t>
+          <t>[49312.49, 47422.57, 49224.15]</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>[54175.0, 48842.0, 48503.5]</t>
+          <t>[46816.9, 54373.4, 54243.7]</t>
         </is>
       </c>
     </row>
@@ -4366,31 +4366,31 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>6072.26</v>
+        <v>6594.01</v>
       </c>
       <c r="E110" t="n">
-        <v>5982.95</v>
+        <v>6547.06</v>
       </c>
       <c r="F110" t="n">
-        <v>12.47</v>
+        <v>11.93</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>[53877.81, 53989.44, 54422.22]</t>
+          <t>[46988.6, 48747.28, 49282.23]</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>[48842.0, 48503.5, 46995.1]</t>
+          <t>[54373.4, 54243.7, 56042.2]</t>
         </is>
       </c>
     </row>
@@ -4402,31 +4402,31 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>5137.22</v>
+        <v>4596.21</v>
       </c>
       <c r="E111" t="n">
-        <v>5003.15</v>
+        <v>4473.39</v>
       </c>
       <c r="F111" t="n">
-        <v>10.33</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>[53191.04, 53557.68, 54847.94]</t>
+          <t>[49697.92, 50313.86, 51838.76]</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>[48503.5, 46995.1, 51088.6]</t>
+          <t>[54243.7, 56042.2, 54984.8]</t>
         </is>
       </c>
     </row>
@@ -4438,31 +4438,31 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11224.61</v>
+        <v>9817.42</v>
       </c>
       <c r="E112" t="n">
-        <v>10481.11</v>
+        <v>8796.25</v>
       </c>
       <c r="F112" t="n">
-        <v>30.61</v>
+        <v>26.13</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>[20321.18, 20288.26, 32529.63]</t>
+          <t>[30503.28, 26031.87, 18785.3]</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>[35614.2, 30979.0, 37989.2]</t>
+          <t>[34474.8, 33915.9, 33318.5]</t>
         </is>
       </c>
     </row>
@@ -4474,31 +4474,31 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>5872.17</v>
+        <v>10257.11</v>
       </c>
       <c r="E113" t="n">
-        <v>4888.25</v>
+        <v>9760.02</v>
       </c>
       <c r="F113" t="n">
-        <v>15.11</v>
+        <v>29.04</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>[21502.92, 35703.02, 30342.9]</t>
+          <t>[26400.29, 19097.52, 26310.41]</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>[30979.0, 37989.2, 33245.4]</t>
+          <t>[33915.9, 33318.5, 33853.9]</t>
         </is>
       </c>
     </row>
@@ -4510,31 +4510,31 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1283.68</v>
+        <v>9186.299999999999</v>
       </c>
       <c r="E114" t="n">
-        <v>1029.34</v>
+        <v>7914.38</v>
       </c>
       <c r="F114" t="n">
-        <v>3.69</v>
+        <v>23.8</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>[38407.54, 32686.75, 27538.02]</t>
+          <t>[19371.98, 26645.62, 28824.58]</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>[37989.2, 33245.4, 25427.0]</t>
+          <t>[33318.5, 33853.9, 31412.9]</t>
         </is>
       </c>
     </row>
@@ -4546,31 +4546,31 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1472.36</v>
+        <v>8196.17</v>
       </c>
       <c r="E115" t="n">
-        <v>1314.75</v>
+        <v>6762.54</v>
       </c>
       <c r="F115" t="n">
-        <v>4.82</v>
+        <v>20.3</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>[32708.05, 27583.94, 29988.94]</t>
+          <t>[27551.83, 30077.76, 20620.29]</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>[33245.4, 25427.0, 28739.0]</t>
+          <t>[33853.9, 31412.9, 33270.7]</t>
         </is>
       </c>
     </row>
@@ -4582,31 +4582,31 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>2707.93</v>
+        <v>8181.24</v>
       </c>
       <c r="E116" t="n">
-        <v>2420.87</v>
+        <v>6747.98</v>
       </c>
       <c r="F116" t="n">
-        <v>8.109999999999999</v>
+        <v>22.55</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>[27493.66, 29882.92, 29136.87]</t>
+          <t>[30386.8, 20915.66, 18335.21]</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>[25427.0, 28739.0, 33188.9]</t>
+          <t>[31412.9, 33270.7, 25198.0]</t>
         </is>
       </c>
     </row>
@@ -4618,31 +4618,31 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>3462.18</v>
+        <v>8446.07</v>
       </c>
       <c r="E117" t="n">
-        <v>3104.85</v>
+        <v>7803.84</v>
       </c>
       <c r="F117" t="n">
-        <v>9.35</v>
+        <v>26.39</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>[29679.19, 28926.85, 30362.49]</t>
+          <t>[21069.87, 18518.35, 32874.34]</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>[28739.0, 33188.9, 34474.8]</t>
+          <t>[33270.7, 25198.0, 28343.3]</t>
         </is>
       </c>
     </row>
@@ -4654,31 +4654,31 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>5971.02</v>
+        <v>5482.84</v>
       </c>
       <c r="E118" t="n">
-        <v>5694.17</v>
+        <v>5401.73</v>
       </c>
       <c r="F118" t="n">
-        <v>16.82</v>
+        <v>19.03</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>[28705.13, 30110.76, 25681.21]</t>
+          <t>[19266.69, 34535.65, 30796.98]</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>[33188.9, 34474.8, 33915.9]</t>
+          <t>[25198.0, 28343.3, 34878.5]</t>
         </is>
       </c>
     </row>
@@ -4690,31 +4690,31 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>9817.42</v>
+        <v>6150.02</v>
       </c>
       <c r="E119" t="n">
-        <v>8796.25</v>
+        <v>5568.93</v>
       </c>
       <c r="F119" t="n">
-        <v>26.13</v>
+        <v>17.7</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>[30503.28, 26031.87, 18785.3]</t>
+          <t>[36648.56, 32822.28, 29099.99]</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>[34474.8, 33915.9, 33318.5]</t>
+          <t>[28343.3, 34878.5, 35445.3]</t>
         </is>
       </c>
     </row>
@@ -4726,31 +4726,31 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>10257.11</v>
+        <v>4590.05</v>
       </c>
       <c r="E120" t="n">
-        <v>9760.02</v>
+        <v>4134.11</v>
       </c>
       <c r="F120" t="n">
-        <v>29.04</v>
+        <v>11.87</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>[26400.29, 19097.52, 26310.41]</t>
+          <t>[32164.02, 28490.67, 30620.27]</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>[33915.9, 33318.5, 33853.9]</t>
+          <t>[34878.5, 35445.3, 33353.5]</t>
         </is>
       </c>
     </row>
@@ -4762,31 +4762,31 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>9186.299999999999</v>
+        <v>3565.23</v>
       </c>
       <c r="E121" t="n">
-        <v>7914.38</v>
+        <v>2550.38</v>
       </c>
       <c r="F121" t="n">
-        <v>23.8</v>
+        <v>7.3</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>[19371.98, 26645.62, 28824.58]</t>
+          <t>[29469.73, 31801.08, 32074.15]</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>[33318.5, 33853.9, 31412.9]</t>
+          <t>[35445.3, 33353.5, 32197.3]</t>
         </is>
       </c>
     </row>
@@ -4798,31 +4798,31 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>5.82</v>
+        <v>45.02</v>
       </c>
       <c r="E122" t="n">
-        <v>5.47</v>
+        <v>43.58</v>
       </c>
       <c r="F122" t="n">
-        <v>1.74</v>
+        <v>5.53</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>[304.35, 316.81, 333.63]</t>
+          <t>[842.15, 892.92, 704.23]</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>[307.6, 308.7, 328.6]</t>
+          <t>[784.7, 863.1, 747.7]</t>
         </is>
       </c>
     </row>
@@ -4834,31 +4834,31 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>14.28</v>
+        <v>39.26</v>
       </c>
       <c r="E123" t="n">
-        <v>11.5</v>
+        <v>38.33</v>
       </c>
       <c r="F123" t="n">
-        <v>2.49</v>
+        <v>5.18</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>[315.34, 333.05, 565.0]</t>
+          <t>[889.67, 701.37, 629.02]</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>[308.7, 328.6, 588.4]</t>
+          <t>[863.1, 747.7, 671.1]</t>
         </is>
       </c>
     </row>
@@ -4870,31 +4870,31 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>15.94</v>
+        <v>50.06</v>
       </c>
       <c r="E124" t="n">
-        <v>9.92</v>
+        <v>49.53</v>
       </c>
       <c r="F124" t="n">
-        <v>1.77</v>
+        <v>7.04</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>[330.48, 560.85, 620.85]</t>
+          <t>[701.22, 628.51, 636.28]</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>[328.6, 588.4, 620.5]</t>
+          <t>[747.7, 671.1, 695.8]</t>
         </is>
       </c>
     </row>
@@ -4906,31 +4906,31 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>88.84999999999999</v>
+        <v>57.46</v>
       </c>
       <c r="E125" t="n">
-        <v>60.12</v>
+        <v>56.3</v>
       </c>
       <c r="F125" t="n">
-        <v>7.48</v>
+        <v>13.75</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>[562.7, 623.45, 709.79]</t>
+          <t>[629.86, 637.27, 328.12]</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>[588.4, 620.5, 861.5]</t>
+          <t>[671.1, 695.8, 259.0]</t>
         </is>
       </c>
     </row>
@@ -4942,31 +4942,31 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>88.52</v>
+        <v>53.6</v>
       </c>
       <c r="E126" t="n">
-        <v>64.37</v>
+        <v>49.73</v>
       </c>
       <c r="F126" t="n">
-        <v>7.68</v>
+        <v>13.78</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>[626.57, 713.32, 836.15]</t>
+          <t>[638.42, 328.5, 379.0]</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>[620.5, 861.5, 797.3]</t>
+          <t>[695.8, 259.0, 356.7]</t>
         </is>
       </c>
     </row>
@@ -4978,31 +4978,31 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>93.89</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="E127" t="n">
-        <v>80.20999999999999</v>
+        <v>60.89</v>
       </c>
       <c r="F127" t="n">
-        <v>9.630000000000001</v>
+        <v>18.29</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>[712.83, 835.69, 838.27]</t>
+          <t>[330.53, 383.56, 342.93]</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>[861.5, 797.3, 784.7]</t>
+          <t>[259.0, 356.7, 427.2]</t>
         </is>
       </c>
     </row>
@@ -5014,31 +5014,31 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>47.15</v>
+        <v>83.98</v>
       </c>
       <c r="E128" t="n">
-        <v>45.8</v>
+        <v>74.41</v>
       </c>
       <c r="F128" t="n">
-        <v>5.68</v>
+        <v>14.45</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>[840.19, 845.44, 896.88]</t>
+          <t>[377.83, 338.09, 568.7]</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>[797.3, 784.7, 863.1]</t>
+          <t>[356.7, 427.2, 681.7]</t>
         </is>
       </c>
     </row>
@@ -5050,31 +5050,31 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>45.02</v>
+        <v>107.59</v>
       </c>
       <c r="E129" t="n">
-        <v>43.58</v>
+        <v>106.99</v>
       </c>
       <c r="F129" t="n">
-        <v>5.53</v>
+        <v>17.92</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>[842.15, 892.92, 704.23]</t>
+          <t>[336.22, 565.95, 623.25]</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>[784.7, 863.1, 747.7]</t>
+          <t>[427.2, 681.7, 737.5]</t>
         </is>
       </c>
     </row>
@@ -5086,31 +5086,31 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>39.26</v>
+        <v>104.02</v>
       </c>
       <c r="E130" t="n">
-        <v>38.33</v>
+        <v>103.96</v>
       </c>
       <c r="F130" t="n">
-        <v>5.18</v>
+        <v>13.96</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>[889.67, 701.37, 629.02]</t>
+          <t>[574.23, 632.23, 738.67]</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>[863.1, 747.7, 671.1]</t>
+          <t>[681.7, 737.5, 837.8]</t>
         </is>
       </c>
     </row>
@@ -5122,31 +5122,31 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>50.06</v>
+        <v>79.56</v>
       </c>
       <c r="E131" t="n">
-        <v>49.53</v>
+        <v>66.06</v>
       </c>
       <c r="F131" t="n">
-        <v>7.04</v>
+        <v>8.43</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>[701.22, 628.51, 636.28]</t>
+          <t>[637.12, 743.45, 805.44]</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>[747.7, 671.1, 695.8]</t>
+          <t>[737.5, 837.8, 808.9]</t>
         </is>
       </c>
     </row>
@@ -5158,31 +5158,31 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>15.27</v>
+        <v>28.62</v>
       </c>
       <c r="E132" t="n">
-        <v>14.53</v>
+        <v>28.36</v>
       </c>
       <c r="F132" t="n">
-        <v>42.41</v>
+        <v>43.28</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>[25.33, 12.72, 21.78]</t>
+          <t>[37.56, 37.9, 35.27]</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>[33.7, 28.1, 41.6]</t>
+          <t>[64.1, 62.7, 69.0]</t>
         </is>
       </c>
     </row>
@@ -5194,31 +5194,31 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>21.9</v>
+        <v>29.51</v>
       </c>
       <c r="E133" t="n">
-        <v>20.86</v>
+        <v>28.84</v>
       </c>
       <c r="F133" t="n">
-        <v>48.9</v>
+        <v>47.58</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>[13.77, 23.42, 27.75]</t>
+          <t>[34.92, 32.0, 26.77]</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>[28.1, 41.6, 57.8]</t>
+          <t>[62.7, 69.0, 48.5]</t>
         </is>
       </c>
     </row>
@@ -5230,31 +5230,31 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>27.32</v>
+        <v>21.59</v>
       </c>
       <c r="E134" t="n">
-        <v>26.51</v>
+        <v>19.52</v>
       </c>
       <c r="F134" t="n">
-        <v>49.82</v>
+        <v>34.93</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>[24.3, 27.9, 25.25]</t>
+          <t>[37.18, 31.37, 31.5]</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>[41.6, 57.8, 57.6]</t>
+          <t>[69.0, 48.5, 41.1]</t>
         </is>
       </c>
     </row>
@@ -5266,31 +5266,31 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>44.19</v>
+        <v>15.22</v>
       </c>
       <c r="E135" t="n">
-        <v>41.19</v>
+        <v>14.22</v>
       </c>
       <c r="F135" t="n">
-        <v>56.41</v>
+        <v>34.23</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>[29.31, 26.26, 33.55]</t>
+          <t>[27.7, 26.73, 22.7]</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>[57.8, 57.6, 97.3]</t>
+          <t>[48.5, 41.1, 30.2]</t>
         </is>
       </c>
     </row>
@@ -5302,31 +5302,31 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>51.48</v>
+        <v>11.23</v>
       </c>
       <c r="E136" t="n">
-        <v>49.68</v>
+        <v>10.59</v>
       </c>
       <c r="F136" t="n">
-        <v>59.31</v>
+        <v>31.83</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>[25.89, 33.13, 40.23]</t>
+          <t>[25.22, 22.11, 18.12]</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>[57.6, 97.3, 93.4]</t>
+          <t>[41.1, 30.2, 25.9]</t>
         </is>
       </c>
     </row>
@@ -5338,31 +5338,31 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>45.05</v>
+        <v>9.83</v>
       </c>
       <c r="E137" t="n">
-        <v>43.74</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="F137" t="n">
-        <v>50.97</v>
+        <v>28.96</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>[40.64, 49.13, 33.8]</t>
+          <t>[23.43, 18.66, 24.07]</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>[97.3, 93.4, 64.1]</t>
+          <t>[30.2, 25.9, 37.9]</t>
         </is>
       </c>
     </row>
@@ -5374,31 +5374,31 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>35.67</v>
+        <v>16.74</v>
       </c>
       <c r="E138" t="n">
-        <v>34.94</v>
+        <v>15.21</v>
       </c>
       <c r="F138" t="n">
-        <v>47.49</v>
+        <v>37.28</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>[48.33, 33.39, 33.65]</t>
+          <t>[18.42, 24.21, 27.75]</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>[93.4, 64.1, 62.7]</t>
+          <t>[25.9, 37.9, 52.2]</t>
         </is>
       </c>
     </row>
@@ -5410,31 +5410,31 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>28.62</v>
+        <v>22.8</v>
       </c>
       <c r="E139" t="n">
-        <v>28.36</v>
+        <v>21.95</v>
       </c>
       <c r="F139" t="n">
-        <v>43.28</v>
+        <v>44.61</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>[37.56, 37.9, 35.27]</t>
+          <t>[24.39, 27.97, 26.19]</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>[64.1, 62.7, 69.0]</t>
+          <t>[37.9, 52.2, 54.3]</t>
         </is>
       </c>
     </row>
@@ -5446,31 +5446,31 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>29.51</v>
+        <v>38.14</v>
       </c>
       <c r="E140" t="n">
-        <v>28.84</v>
+        <v>35.8</v>
       </c>
       <c r="F140" t="n">
-        <v>47.58</v>
+        <v>53.77</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>[34.92, 32.0, 26.77]</t>
+          <t>[27.61, 25.78, 33.72]</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>[62.7, 69.0, 48.5]</t>
+          <t>[52.2, 54.3, 88.0]</t>
         </is>
       </c>
     </row>
@@ -5482,31 +5482,31 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>21.59</v>
+        <v>36.73</v>
       </c>
       <c r="E141" t="n">
-        <v>19.52</v>
+        <v>35.36</v>
       </c>
       <c r="F141" t="n">
-        <v>34.93</v>
+        <v>45.4</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>[37.18, 31.37, 31.5]</t>
+          <t>[32.24, 42.15, 49.62]</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>[69.0, 48.5, 41.1]</t>
+          <t>[54.3, 88.0, 87.8]</t>
         </is>
       </c>
     </row>
@@ -5518,31 +5518,31 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1171.01</v>
+        <v>1397.88</v>
       </c>
       <c r="E142" t="n">
-        <v>1109.78</v>
+        <v>1043.88</v>
       </c>
       <c r="F142" t="n">
-        <v>39.55</v>
+        <v>23.18</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>[3941.84, 3866.71, 3797.72]</t>
+          <t>[5808.0, 5190.21, 6532.24]</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>[2308.2, 2958.4, 4585.1]</t>
+          <t>[6256.2, 5516.8, 4175.4]</t>
         </is>
       </c>
     </row>
@@ -5554,31 +5554,31 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1230.43</v>
+        <v>1702.02</v>
       </c>
       <c r="E143" t="n">
-        <v>1132.05</v>
+        <v>1451.33</v>
       </c>
       <c r="F143" t="n">
-        <v>25.77</v>
+        <v>39.32</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>[3466.61, 3379.39, 3288.58]</t>
+          <t>[5244.97, 5839.15, 5723.1]</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>[2958.4, 4585.1, 4970.8]</t>
+          <t>[5516.8, 4175.4, 3304.7]</t>
         </is>
       </c>
     </row>
@@ -5590,31 +5590,31 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>2497.61</v>
+        <v>2726.93</v>
       </c>
       <c r="E144" t="n">
-        <v>2272.1</v>
+        <v>2353.33</v>
       </c>
       <c r="F144" t="n">
-        <v>39.75</v>
+        <v>64.27</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>[3273.71, 3178.15, 3088.34]</t>
+          <t>[7141.08, 6953.65, 4362.25]</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>[4585.1, 4970.8, 6800.6]</t>
+          <t>[4175.4, 3304.7, 3916.9]</t>
         </is>
       </c>
     </row>
@@ -5626,31 +5626,31 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>3082.06</v>
+        <v>789.12</v>
       </c>
       <c r="E145" t="n">
-        <v>2932.68</v>
+        <v>680.41</v>
       </c>
       <c r="F145" t="n">
-        <v>45.74</v>
+        <v>19.63</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>[3374.36, 3292.16, 3209.33]</t>
+          <t>[4208.58, 2898.58, 2029.97]</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>[4970.8, 6800.6, 6902.5]</t>
+          <t>[3304.7, 3916.9, 2149.0]</t>
         </is>
       </c>
     </row>
@@ -5662,31 +5662,31 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>3467.29</v>
+        <v>978.4400000000001</v>
       </c>
       <c r="E146" t="n">
-        <v>3463.46</v>
+        <v>778.63</v>
       </c>
       <c r="F146" t="n">
-        <v>50.03</v>
+        <v>23.4</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>[3528.27, 3454.72, 3385.01]</t>
+          <t>[2305.29, 1707.93, 3038.99]</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>[6800.6, 6902.5, 7055.3]</t>
+          <t>[3916.9, 2149.0, 3322.2]</t>
         </is>
       </c>
     </row>
@@ -5698,31 +5698,31 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>2958.89</v>
+        <v>258.66</v>
       </c>
       <c r="E147" t="n">
-        <v>2942.19</v>
+        <v>178.62</v>
       </c>
       <c r="F147" t="n">
-        <v>43.54</v>
+        <v>4.55</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>[3849.66, 3796.14, 3741.63]</t>
+          <t>[2097.5, 3280.98, 4866.34]</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>[6902.5, 7055.3, 6256.2]</t>
+          <t>[2149.0, 3322.2, 4423.2]</t>
         </is>
       </c>
     </row>
@@ -5734,31 +5734,31 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1834.49</v>
+        <v>276.64</v>
       </c>
       <c r="E148" t="n">
-        <v>1820.03</v>
+        <v>245.21</v>
       </c>
       <c r="F148" t="n">
-        <v>29.66</v>
+        <v>5.69</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>[5513.76, 4442.09, 3412.36]</t>
+          <t>[3186.66, 4848.06, 5334.41]</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>[7055.3, 6256.2, 5516.8]</t>
+          <t>[3322.2, 4423.2, 5159.2]</t>
         </is>
       </c>
     </row>
@@ -5770,31 +5770,31 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1397.88</v>
+        <v>1031.36</v>
       </c>
       <c r="E149" t="n">
-        <v>1043.88</v>
+        <v>798.5599999999999</v>
       </c>
       <c r="F149" t="n">
-        <v>23.18</v>
+        <v>14.74</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>[5808.0, 5190.21, 6532.24]</t>
+          <t>[4880.55, 5385.61, 7514.33]</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>[6256.2, 5516.8, 4175.4]</t>
+          <t>[4423.2, 5159.2, 5802.4]</t>
         </is>
       </c>
     </row>
@@ -5806,31 +5806,31 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1702.02</v>
+        <v>882.03</v>
       </c>
       <c r="E150" t="n">
-        <v>1451.33</v>
+        <v>735</v>
       </c>
       <c r="F150" t="n">
-        <v>39.32</v>
+        <v>12.17</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>[5244.97, 5839.15, 5723.1]</t>
+          <t>[5070.26, 7069.18, 7405.87]</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>[5516.8, 4175.4, 3304.7]</t>
+          <t>[5159.2, 5802.4, 6556.6]</t>
         </is>
       </c>
     </row>
@@ -5842,31 +5842,31 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>2726.93</v>
+        <v>939.36</v>
       </c>
       <c r="E151" t="n">
-        <v>2353.33</v>
+        <v>789.09</v>
       </c>
       <c r="F151" t="n">
-        <v>64.27</v>
+        <v>12.85</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>[7141.08, 6953.65, 4362.25]</t>
+          <t>[7136.63, 7481.41, 7349.96]</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>[4175.4, 3304.7, 3916.9]</t>
+          <t>[5802.4, 6556.6, 7458.2]</t>
         </is>
       </c>
     </row>
@@ -5878,31 +5878,31 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1998.31</v>
+        <v>7141.57</v>
       </c>
       <c r="E152" t="n">
-        <v>1859.7</v>
+        <v>4729.36</v>
       </c>
       <c r="F152" t="n">
-        <v>6.99</v>
+        <v>17.23</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>[25095.13, 24581.1, 24109.76]</t>
+          <t>[39415.02, 29625.07, 31019.38]</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>[26494.8, 25868.7, 27001.6]</t>
+          <t>[27169.4, 29416.8, 29285.2]</t>
         </is>
       </c>
     </row>
@@ -5914,31 +5914,31 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1934.32</v>
+        <v>6540.98</v>
       </c>
       <c r="E153" t="n">
-        <v>1809.16</v>
+        <v>5710.44</v>
       </c>
       <c r="F153" t="n">
-        <v>6.82</v>
+        <v>19.58</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>[25015.43, 24582.07, 24127.13]</t>
+          <t>[20549.01, 22363.04, 28352.96]</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>[25868.7, 27001.6, 26281.8]</t>
+          <t>[29416.8, 29285.2, 27011.6]</t>
         </is>
       </c>
     </row>
@@ -5950,31 +5950,31 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>3326.06</v>
+        <v>9557.620000000001</v>
       </c>
       <c r="E154" t="n">
-        <v>2993.32</v>
+        <v>8291.66</v>
       </c>
       <c r="F154" t="n">
-        <v>10.7</v>
+        <v>30.02</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>[24882.09, 24458.27, 24054.99]</t>
+          <t>[26495.44, 34708.86, 42044.97]</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>[27001.6, 26281.8, 29091.9]</t>
+          <t>[29285.2, 27011.6, 27657.0]</t>
         </is>
       </c>
     </row>
@@ -5986,31 +5986,31 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>2991.43</v>
+        <v>9796.799999999999</v>
       </c>
       <c r="E155" t="n">
-        <v>2664.49</v>
+        <v>8648.09</v>
       </c>
       <c r="F155" t="n">
-        <v>9.33</v>
+        <v>31.95</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>[25529.43, 25293.76, 25052.53]</t>
+          <t>[33877.57, 42618.3, 29310.8]</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>[26281.8, 29091.9, 28495.5]</t>
+          <t>[27011.6, 27657.0, 25193.8]</t>
         </is>
       </c>
     </row>
@@ -6022,31 +6022,31 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>2679.13</v>
+        <v>10383.07</v>
       </c>
       <c r="E156" t="n">
-        <v>2408.02</v>
+        <v>10097.32</v>
       </c>
       <c r="F156" t="n">
-        <v>8.449999999999999</v>
+        <v>36.81</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>[25656.32, 25471.27, 25293.46]</t>
+          <t>[39730.22, 18503.12, 40189.97]</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>[29091.9, 28495.5, 26057.7]</t>
+          <t>[27657.0, 25193.8, 28661.9]</t>
         </is>
       </c>
     </row>
@@ -6058,31 +6058,31 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1039.07</v>
+        <v>7205.03</v>
       </c>
       <c r="E157" t="n">
-        <v>843.91</v>
+        <v>6237.77</v>
       </c>
       <c r="F157" t="n">
-        <v>3.08</v>
+        <v>23.23</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>[27036.44, 27111.17, 27188.6]</t>
+          <t>[16537.33, 37578.31, 25949.26]</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>[28495.5, 26057.7, 27169.4]</t>
+          <t>[25193.8, 28661.9, 27089.7]</t>
         </is>
       </c>
     </row>
@@ -6094,31 +6094,31 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>8444.280000000001</v>
+        <v>5863.21</v>
       </c>
       <c r="E158" t="n">
-        <v>7000.43</v>
+        <v>4617.83</v>
       </c>
       <c r="F158" t="n">
-        <v>24.87</v>
+        <v>16.3</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>[19696.07, 25606.64, 16339.9]</t>
+          <t>[38180.4, 30508.93, 30702.87]</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>[26057.7, 27169.4, 29416.8]</t>
+          <t>[28661.9, 27089.7, 29787.1]</t>
         </is>
       </c>
     </row>
@@ -6130,31 +6130,31 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>7141.57</v>
+        <v>1502.2</v>
       </c>
       <c r="E159" t="n">
-        <v>4729.36</v>
+        <v>1430.9</v>
       </c>
       <c r="F159" t="n">
-        <v>17.23</v>
+        <v>5.06</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>[39415.02, 29625.07, 31019.38]</t>
+          <t>[27959.14, 27797.56, 28475.83]</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>[27169.4, 29416.8, 29285.2]</t>
+          <t>[27089.7, 29787.1, 27042.1]</t>
         </is>
       </c>
     </row>
@@ -6166,31 +6166,31 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>6540.98</v>
+        <v>1560.35</v>
       </c>
       <c r="E160" t="n">
-        <v>5710.44</v>
+        <v>1108.09</v>
       </c>
       <c r="F160" t="n">
-        <v>19.58</v>
+        <v>3.8</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>[20549.01, 22363.04, 28352.96]</t>
+          <t>[27176.27, 27740.26, 28024.1]</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>[29416.8, 29285.2, 27011.6]</t>
+          <t>[29787.1, 27042.1, 28008.8]</t>
         </is>
       </c>
     </row>
@@ -6202,31 +6202,31 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>9557.620000000001</v>
+        <v>2081.31</v>
       </c>
       <c r="E161" t="n">
-        <v>8291.66</v>
+        <v>2032.83</v>
       </c>
       <c r="F161" t="n">
-        <v>30.02</v>
+        <v>7.34</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>[26495.44, 34708.86, 42044.97]</t>
+          <t>[29021.21, 29523.52, 25382.53]</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>[29285.2, 27011.6, 27657.0]</t>
+          <t>[27042.1, 28008.8, 27987.2]</t>
         </is>
       </c>
     </row>
@@ -6238,31 +6238,31 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>317.49</v>
+        <v>1172.88</v>
       </c>
       <c r="E162" t="n">
-        <v>291.07</v>
+        <v>867.71</v>
       </c>
       <c r="F162" t="n">
-        <v>21.94</v>
+        <v>88.43000000000001</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>[1673.93, 1681.66, 1688.92]</t>
+          <t>[2913.04, 1695.29, 1562.57]</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>[1343.0, 1259.1, 1569.2]</t>
+          <t>[973.5, 1757.9, 961.6]</t>
         </is>
       </c>
     </row>
@@ -6274,31 +6274,31 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>250.97</v>
+        <v>430.04</v>
       </c>
       <c r="E163" t="n">
-        <v>221.08</v>
+        <v>397.01</v>
       </c>
       <c r="F163" t="n">
-        <v>18.05</v>
+        <v>42.09</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>[1523.44, 1510.32, 1496.42]</t>
+          <t>[1594.4, 1483.81, 1311.63]</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>[1259.1, 1569.2, 1156.4]</t>
+          <t>[1757.9, 961.6, 806.3]</t>
         </is>
       </c>
     </row>
@@ -6310,31 +6310,31 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>195.27</v>
+        <v>639.79</v>
       </c>
       <c r="E164" t="n">
-        <v>192.97</v>
+        <v>628.45</v>
       </c>
       <c r="F164" t="n">
-        <v>15.4</v>
+        <v>56.22</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>[1411.22, 1387.4, 1364.73]</t>
+          <t>[1512.13, 1343.29, 982.76]</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>[1569.2, 1156.4, 1174.8]</t>
+          <t>[961.6, 806.3, 1780.6]</t>
         </is>
       </c>
     </row>
@@ -6346,31 +6346,31 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>388.44</v>
+        <v>628.27</v>
       </c>
       <c r="E165" t="n">
-        <v>357.73</v>
+        <v>592.3200000000001</v>
       </c>
       <c r="F165" t="n">
-        <v>24.1</v>
+        <v>44.73</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>[1426.77, 1406.93, 1386.72]</t>
+          <t>[1279.14, 893.79, 1204.48]</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>[1156.4, 1174.8, 1957.4]</t>
+          <t>[806.3, 1780.6, 1621.8]</t>
         </is>
       </c>
     </row>
@@ -6382,31 +6382,31 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>381.24</v>
+        <v>917.39</v>
       </c>
       <c r="E166" t="n">
-        <v>273.69</v>
+        <v>885.67</v>
       </c>
       <c r="F166" t="n">
-        <v>16.01</v>
+        <v>49.38</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>[1343.26, 1319.09, 1296.11]</t>
+          <t>[779.23, 1069.22, 804.05]</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>[1174.8, 1957.4, 1310.4]</t>
+          <t>[1780.6, 1621.8, 1907.1]</t>
         </is>
       </c>
     </row>
@@ -6418,31 +6418,31 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>416.59</v>
+        <v>1162.65</v>
       </c>
       <c r="E167" t="n">
-        <v>327.17</v>
+        <v>1054.47</v>
       </c>
       <c r="F167" t="n">
-        <v>21.68</v>
+        <v>48.21</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>[1288.11, 1263.74, 1239.05]</t>
+          <t>[1200.01, 780.37, 1097.42]</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>[1957.4, 1310.4, 973.5]</t>
+          <t>[1621.8, 1907.1, 2712.3]</t>
         </is>
       </c>
     </row>
@@ -6454,31 +6454,31 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>2158.02</v>
+        <v>1350.03</v>
       </c>
       <c r="E168" t="n">
-        <v>1843.82</v>
+        <v>1340.46</v>
       </c>
       <c r="F168" t="n">
-        <v>165.31</v>
+        <v>59.97</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>[3437.64, 4026.84, 2108.77]</t>
+          <t>[724.26, 1151.55, 839.72]</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>[1310.4, 973.5, 1757.9]</t>
+          <t>[1907.1, 2712.3, 2117.5]</t>
         </is>
       </c>
     </row>
@@ -6490,31 +6490,31 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1172.88</v>
+        <v>1251.7</v>
       </c>
       <c r="E169" t="n">
-        <v>867.71</v>
+        <v>1246.16</v>
       </c>
       <c r="F169" t="n">
-        <v>88.43000000000001</v>
+        <v>52.95</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>[2913.04, 1695.29, 1562.57]</t>
+          <t>[1300.39, 967.51, 1065.33]</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>[973.5, 1757.9, 961.6]</t>
+          <t>[2712.3, 2117.5, 2241.9]</t>
         </is>
       </c>
     </row>
@@ -6526,31 +6526,31 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>430.04</v>
+        <v>1323.39</v>
       </c>
       <c r="E170" t="n">
-        <v>397.01</v>
+        <v>1153.11</v>
       </c>
       <c r="F170" t="n">
-        <v>42.09</v>
+        <v>35.95</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>[1594.4, 1483.81, 1311.63]</t>
+          <t>[1379.86, 1590.34, 2640.67]</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>[1757.9, 961.6, 806.3]</t>
+          <t>[2117.5, 2241.9, 4710.8]</t>
         </is>
       </c>
     </row>
@@ -6562,31 +6562,31 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>639.79</v>
+        <v>731.67</v>
       </c>
       <c r="E171" t="n">
-        <v>628.45</v>
+        <v>614.98</v>
       </c>
       <c r="F171" t="n">
-        <v>56.22</v>
+        <v>20.43</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>[1512.13, 1343.29, 982.76]</t>
+          <t>[2187.53, 3815.99, 3142.85]</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>[961.6, 806.3, 1780.6]</t>
+          <t>[2241.9, 4710.8, 2247.1]</t>
         </is>
       </c>
     </row>
@@ -6598,31 +6598,31 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>2944.17</v>
+        <v>767.42</v>
       </c>
       <c r="E172" t="n">
-        <v>2940.45</v>
+        <v>652.79</v>
       </c>
       <c r="F172" t="n">
-        <v>18.45</v>
+        <v>3.8</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>[13103.89, 12185.11, 13846.16]</t>
+          <t>[18342.7, 18460.25, 15312.59]</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>[16000.7, 15324.7, 16631.1]</t>
+          <t>[18689.8, 18071.9, 16535.5]</t>
         </is>
       </c>
     </row>
@@ -6634,31 +6634,31 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>2212.85</v>
+        <v>1016.16</v>
       </c>
       <c r="E173" t="n">
-        <v>2110.76</v>
+        <v>943.84</v>
       </c>
       <c r="F173" t="n">
-        <v>13.16</v>
+        <v>5.74</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>[12494.26, 14357.05, 15519.3]</t>
+          <t>[18483.47, 15338.0, 14676.76]</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>[15324.7, 16631.1, 16747.1]</t>
+          <t>[18071.9, 16535.5, 15899.2]</t>
         </is>
       </c>
     </row>
@@ -6670,31 +6670,31 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1069.78</v>
+        <v>1151.73</v>
       </c>
       <c r="E174" t="n">
-        <v>924</v>
+        <v>1145.76</v>
       </c>
       <c r="F174" t="n">
-        <v>5.5</v>
+        <v>7.26</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>[14947.34, 16147.79, 16925.07]</t>
+          <t>[15319.34, 14658.8, 13854.19]</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>[16631.1, 16747.1, 17414.0]</t>
+          <t>[16535.5, 15899.2, 14834.9]</t>
         </is>
       </c>
     </row>
@@ -6706,31 +6706,31 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>620.89</v>
+        <v>1600.38</v>
       </c>
       <c r="E175" t="n">
-        <v>597.0700000000001</v>
+        <v>1484.35</v>
       </c>
       <c r="F175" t="n">
-        <v>3.35</v>
+        <v>9.68</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>[16201.91, 16994.72, 18005.67]</t>
+          <t>[14699.77, 13898.03, 12938.36]</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>[16747.1, 17414.0, 18832.4]</t>
+          <t>[15899.2, 14834.9, 15255.1]</t>
         </is>
       </c>
     </row>
@@ -6742,31 +6742,31 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>480.13</v>
+        <v>1450.22</v>
       </c>
       <c r="E176" t="n">
-        <v>391.84</v>
+        <v>1292.97</v>
       </c>
       <c r="F176" t="n">
-        <v>2.13</v>
+        <v>8.75</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>[17056.86, 18084.72, 18584.0]</t>
+          <t>[13971.09, 13034.16, 12710.94]</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>[17414.0, 18832.4, 18654.7]</t>
+          <t>[14834.9, 15255.1, 13505.1]</t>
         </is>
       </c>
     </row>
@@ -6778,31 +6778,31 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>479.01</v>
+        <v>1327.31</v>
       </c>
       <c r="E177" t="n">
-        <v>393.73</v>
+        <v>1110.96</v>
       </c>
       <c r="F177" t="n">
-        <v>2.1</v>
+        <v>7.51</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>[18107.89, 18598.36, 18289.47]</t>
+          <t>[13122.56, 12812.46, 14265.99]</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>[18832.4, 18654.7, 18689.8]</t>
+          <t>[15255.1, 13505.1, 14773.7]</t>
         </is>
       </c>
     </row>
@@ -6814,31 +6814,31 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>306.19</v>
+        <v>663.8</v>
       </c>
       <c r="E178" t="n">
-        <v>259.12</v>
+        <v>583.36</v>
       </c>
       <c r="F178" t="n">
-        <v>1.41</v>
+        <v>3.8</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>[18688.35, 18360.31, 18486.1]</t>
+          <t>[13012.81, 14524.63, 15623.98]</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>[18654.7, 18689.8, 18071.9]</t>
+          <t>[13505.1, 14773.7, 16632.7]</t>
         </is>
       </c>
     </row>
@@ -6850,31 +6850,31 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>767.42</v>
+        <v>634.37</v>
       </c>
       <c r="E179" t="n">
-        <v>652.79</v>
+        <v>548.5599999999999</v>
       </c>
       <c r="F179" t="n">
-        <v>3.8</v>
+        <v>3.36</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>[18342.7, 18460.25, 15312.59]</t>
+          <t>[14665.37, 15780.94, 16886.6]</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>[18689.8, 18071.9, 16535.5]</t>
+          <t>[14773.7, 16632.7, 16201.0]</t>
         </is>
       </c>
     </row>
@@ -6886,31 +6886,31 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1016.16</v>
+        <v>918.87</v>
       </c>
       <c r="E180" t="n">
-        <v>943.84</v>
+        <v>903.23</v>
       </c>
       <c r="F180" t="n">
-        <v>5.74</v>
+        <v>5.46</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>[18483.47, 15338.0, 14676.76]</t>
+          <t>[15851.01, 16987.1, 17841.51]</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>[18071.9, 16535.5, 15899.2]</t>
+          <t>[16632.7, 16201.0, 16699.6]</t>
         </is>
       </c>
     </row>
@@ -6922,31 +6922,31 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1151.73</v>
+        <v>990.71</v>
       </c>
       <c r="E181" t="n">
-        <v>1145.76</v>
+        <v>893.88</v>
       </c>
       <c r="F181" t="n">
-        <v>7.26</v>
+        <v>5.34</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>[15319.34, 14658.8, 13854.19]</t>
+          <t>[17188.34, 18063.65, 18403.94]</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>[16535.5, 15899.2, 14834.9]</t>
+          <t>[16201.0, 16699.6, 18734.2]</t>
         </is>
       </c>
     </row>
@@ -6958,31 +6958,31 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>12877.6</v>
+        <v>7947.63</v>
       </c>
       <c r="E182" t="n">
-        <v>12424.02</v>
+        <v>7202.34</v>
       </c>
       <c r="F182" t="n">
-        <v>27.08</v>
+        <v>14.29</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>[33731.71, 31029.12, 33780.72]</t>
+          <t>[61524.44, 48948.14, 36950.07]</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>[41455.0, 45002.3, 49356.3]</t>
+          <t>[53762.5, 51783.9, 47959.4]</t>
         </is>
       </c>
     </row>
@@ -6994,31 +6994,31 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>11043.21</v>
+        <v>10165.58</v>
       </c>
       <c r="E183" t="n">
-        <v>10154.09</v>
+        <v>9446.379999999999</v>
       </c>
       <c r="F183" t="n">
-        <v>21.42</v>
+        <v>19.59</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>[32282.2, 35654.87, 45058.45]</t>
+          <t>[47647.82, 35946.7, 35161.65]</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>[45002.3, 49356.3, 49099.2]</t>
+          <t>[51783.9, 47959.4, 47352.0]</t>
         </is>
       </c>
     </row>
@@ -7030,31 +7030,31 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>5858.35</v>
+        <v>11409.08</v>
       </c>
       <c r="E184" t="n">
-        <v>3786.56</v>
+        <v>11408.1</v>
       </c>
       <c r="F184" t="n">
-        <v>7.64</v>
+        <v>23.81</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>[39271.27, 49267.24, 50393.69]</t>
+          <t>[36366.35, 35948.22, 37214.02]</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>[49356.3, 49099.2, 51500.3]</t>
+          <t>[47959.4, 47352.0, 48441.5]</t>
         </is>
       </c>
     </row>
@@ -7066,31 +7066,31 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>4447.84</v>
+        <v>10452.5</v>
       </c>
       <c r="E185" t="n">
-        <v>2948.53</v>
+        <v>10446.61</v>
       </c>
       <c r="F185" t="n">
-        <v>5.33</v>
+        <v>21.91</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>[49799.73, 51011.64, 63890.1]</t>
+          <t>[36609.73, 38487.42, 36683.5]</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>[49099.2, 51500.3, 56233.7]</t>
+          <t>[47352.0, 48441.5, 47327.0]</t>
         </is>
       </c>
     </row>
@@ -7102,31 +7102,31 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>11419.96</v>
+        <v>9093.219999999999</v>
       </c>
       <c r="E186" t="n">
-        <v>8859.040000000001</v>
+        <v>9088.799999999999</v>
       </c>
       <c r="F186" t="n">
-        <v>15.4</v>
+        <v>19.51</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>[51721.58, 64727.46, 76123.17]</t>
+          <t>[39734.9, 37942.39, 35090.2]</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>[51500.3, 56233.7, 58261.1]</t>
+          <t>[48441.5, 47327.0, 44265.4]</t>
         </is>
       </c>
     </row>
@@ -7138,31 +7138,31 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>10563.18</v>
+        <v>8717.059999999999</v>
       </c>
       <c r="E187" t="n">
-        <v>9786.27</v>
+        <v>8712.959999999999</v>
       </c>
       <c r="F187" t="n">
-        <v>17.29</v>
+        <v>18.59</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>[62753.76, 73644.51, 61217.83]</t>
+          <t>[38622.67, 35875.52, 40028.34]</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>[56233.7, 58261.1, 53762.5]</t>
+          <t>[47327.0, 44265.4, 49073.0]</t>
         </is>
       </c>
     </row>
@@ -7174,31 +7174,31 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>10837.49</v>
+        <v>7444.72</v>
       </c>
       <c r="E188" t="n">
-        <v>9134.700000000001</v>
+        <v>7175.53</v>
       </c>
       <c r="F188" t="n">
-        <v>16.25</v>
+        <v>15.03</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>[74861.36, 62199.49, 49417.04]</t>
+          <t>[35931.39, 40263.81, 48425.41]</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>[58261.1, 53762.5, 51783.9]</t>
+          <t>[44265.4, 49073.0, 52808.8]</t>
         </is>
       </c>
     </row>
@@ -7210,31 +7210,31 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>7947.63</v>
+        <v>3815.09</v>
       </c>
       <c r="E189" t="n">
-        <v>7202.34</v>
+        <v>2893.87</v>
       </c>
       <c r="F189" t="n">
-        <v>14.29</v>
+        <v>5.74</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>[61524.44, 48948.14, 36950.07]</t>
+          <t>[42665.87, 51555.73, 56239.68]</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>[53762.5, 51783.9, 47959.4]</t>
+          <t>[49073.0, 52808.8, 57261.1]</t>
         </is>
       </c>
     </row>
@@ -7246,31 +7246,31 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>10165.58</v>
+        <v>5247.44</v>
       </c>
       <c r="E190" t="n">
-        <v>9446.379999999999</v>
+        <v>3194.56</v>
       </c>
       <c r="F190" t="n">
-        <v>19.59</v>
+        <v>5.42</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>[47647.82, 35946.7, 35161.65]</t>
+          <t>[52387.31, 57177.58, 68360.17]</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>[51783.9, 47959.4, 47352.0]</t>
+          <t>[52808.8, 57261.1, 59281.5]</t>
         </is>
       </c>
     </row>
@@ -7282,31 +7282,31 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>11409.08</v>
+        <v>7808.32</v>
       </c>
       <c r="E191" t="n">
-        <v>11408.1</v>
+        <v>6696.61</v>
       </c>
       <c r="F191" t="n">
-        <v>23.81</v>
+        <v>10.95</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>[36366.35, 35948.22, 37214.02]</t>
+          <t>[55781.34, 66643.28, 74256.89]</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>[47959.4, 47352.0, 48441.5]</t>
+          <t>[57261.1, 59281.5, 63008.6]</t>
         </is>
       </c>
     </row>
@@ -7318,31 +7318,31 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>2481</v>
+        <v>3202.19</v>
       </c>
       <c r="E192" t="n">
-        <v>1731.28</v>
+        <v>3152.09</v>
       </c>
       <c r="F192" t="n">
-        <v>12.93</v>
+        <v>13.84</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>[16261.64, 16785.16, 21931.22]</t>
+          <t>[20885.52, 18918.41, 19034.81]</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>[16642.4, 12543.1, 21360.2]</t>
+          <t>[23808.0, 22847.1, 21639.9]</t>
         </is>
       </c>
     </row>
@@ -7354,31 +7354,31 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>2510.88</v>
+        <v>2860.21</v>
       </c>
       <c r="E193" t="n">
-        <v>1674.64</v>
+        <v>2788.67</v>
       </c>
       <c r="F193" t="n">
-        <v>12.54</v>
+        <v>12.95</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>[16836.82, 22050.09, 24429.39]</t>
+          <t>[19159.48, 19308.62, 17312.29]</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>[12543.1, 21360.2, 24469.7]</t>
+          <t>[22847.1, 21639.9, 19659.4]</t>
         </is>
       </c>
     </row>
@@ -7390,31 +7390,31 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1263.11</v>
+        <v>2124.47</v>
       </c>
       <c r="E194" t="n">
-        <v>1130.27</v>
+        <v>2122.85</v>
       </c>
       <c r="F194" t="n">
-        <v>4.83</v>
+        <v>10.49</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>[20409.49, 22576.79, 24301.38]</t>
+          <t>[19567.06, 17603.33, 17337.14]</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>[21360.2, 24469.7, 23754.2]</t>
+          <t>[21639.9, 19659.4, 19576.8]</t>
         </is>
       </c>
     </row>
@@ -7426,31 +7426,31 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1202.83</v>
+        <v>2119.38</v>
       </c>
       <c r="E195" t="n">
-        <v>1147.64</v>
+        <v>2113.76</v>
       </c>
       <c r="F195" t="n">
-        <v>4.84</v>
+        <v>10.94</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>[22813.32, 24626.47, 23263.98]</t>
+          <t>[17723.8, 17483.19, 16518.45]</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>[24469.7, 23754.2, 22349.7]</t>
+          <t>[19659.4, 19576.8, 18830.5]</t>
         </is>
       </c>
     </row>
@@ -7462,31 +7462,31 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>907.4299999999999</v>
+        <v>2010.6</v>
       </c>
       <c r="E196" t="n">
-        <v>806.47</v>
+        <v>2006.85</v>
       </c>
       <c r="F196" t="n">
-        <v>3.51</v>
+        <v>11.05</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>[24818.21, 23485.44, 22217.75]</t>
+          <t>[17736.12, 16783.76, 18678.73]</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>[23754.2, 22349.7, 22437.4]</t>
+          <t>[19576.8, 18830.5, 16545.6]</t>
         </is>
       </c>
     </row>
@@ -7498,31 +7498,31 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1782.69</v>
+        <v>2116.19</v>
       </c>
       <c r="E197" t="n">
-        <v>1433.92</v>
+        <v>2108.54</v>
       </c>
       <c r="F197" t="n">
-        <v>6.15</v>
+        <v>11.34</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>[23385.94, 22055.29, 20924.57]</t>
+          <t>[16931.27, 18883.66, 23360.73]</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>[22349.7, 22437.4, 23808.0]</t>
+          <t>[18830.5, 16545.6, 21272.4]</t>
         </is>
       </c>
     </row>
@@ -7534,31 +7534,31 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>2868.38</v>
+        <v>2507.34</v>
       </c>
       <c r="E198" t="n">
-        <v>2454.73</v>
+        <v>2504.18</v>
       </c>
       <c r="F198" t="n">
-        <v>10.58</v>
+        <v>12.57</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>[21997.57, 20853.79, 18876.96]</t>
+          <t>[19193.05, 23796.07, 26098.53]</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>[22437.4, 23808.0, 22847.1]</t>
+          <t>[16545.6, 21272.4, 23757.1]</t>
         </is>
       </c>
     </row>
@@ -7570,31 +7570,31 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>3202.19</v>
+        <v>1677.44</v>
       </c>
       <c r="E199" t="n">
-        <v>3152.09</v>
+        <v>1650.6</v>
       </c>
       <c r="F199" t="n">
-        <v>13.84</v>
+        <v>7.16</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>[20885.52, 18918.41, 19034.81]</t>
+          <t>[23264.13, 25453.3, 26582.97]</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>[23808.0, 22847.1, 21639.9]</t>
+          <t>[21272.4, 23757.1, 25319.1]</t>
         </is>
       </c>
     </row>
@@ -7606,31 +7606,31 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>2860.21</v>
+        <v>1793.09</v>
       </c>
       <c r="E200" t="n">
-        <v>2788.67</v>
+        <v>1642.4</v>
       </c>
       <c r="F200" t="n">
-        <v>12.95</v>
+        <v>6.35</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>[19159.48, 19308.62, 17312.29]</t>
+          <t>[25137.02, 26241.31, 24727.25]</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>[22847.1, 21639.9, 19659.4]</t>
+          <t>[23757.1, 25319.1, 27352.3]</t>
         </is>
       </c>
     </row>
@@ -7642,31 +7642,31 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>2124.47</v>
+        <v>1700.48</v>
       </c>
       <c r="E201" t="n">
-        <v>2122.85</v>
+        <v>1251.28</v>
       </c>
       <c r="F201" t="n">
-        <v>10.49</v>
+        <v>4.68</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>[19567.06, 17603.33, 17337.14]</t>
+          <t>[26057.42, 24506.05, 23291.43]</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>[21639.9, 19659.4, 19576.8]</t>
+          <t>[25319.1, 27352.3, 23460.7]</t>
         </is>
       </c>
     </row>
